--- a/public/data/PUBLICACION CONVOCATORIA.xlsx
+++ b/public/data/PUBLICACION CONVOCATORIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026\ESFM\INSTITUCIONALIZACIÓN\BASE OFICIAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDCC946-6850-4202-A4A0-8837BD926434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EB0230-C2B4-439A-BF55-F7A82B89F86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{928717D9-E10C-4759-930F-0D125842C64E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3644" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3609" uniqueCount="130">
   <si>
     <t>ESFM</t>
   </si>
@@ -407,9 +407,6 @@
     <t>INAMOBILIDAD</t>
   </si>
   <si>
-    <t>COMPULSA</t>
-  </si>
-  <si>
     <t>REPONER CON COMPULSA</t>
   </si>
   <si>
@@ -566,18 +563,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A33032D3-22F0-4889-89B2-2B6957DE8ECA}" name="Tabla5" displayName="Tabla5" ref="A1:J888" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:J888" xr:uid="{A33032D3-22F0-4889-89B2-2B6957DE8ECA}">
-    <filterColumn colId="5">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="9">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J888" xr:uid="{A33032D3-22F0-4889-89B2-2B6957DE8ECA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J888">
     <sortCondition ref="B1:B888"/>
   </sortState>
@@ -959,7 +945,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -982,7 +968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1005,7 +991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1028,7 +1014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1051,7 +1037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1074,7 +1060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1097,7 +1083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1120,7 +1106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1143,7 +1129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1166,7 +1152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1189,7 +1175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1212,7 +1198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1235,7 +1221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1258,7 +1244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1281,7 +1267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1304,7 +1290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1323,11 +1309,9 @@
       <c r="I17" s="5">
         <v>1</v>
       </c>
-      <c r="J17" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1350,7 +1334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1373,7 +1357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1396,7 +1380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1419,7 +1403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1446,7 +1430,7 @@
       </c>
       <c r="J22" s="5"/>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1476,7 +1460,7 @@
       </c>
       <c r="J23" s="5"/>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1499,7 +1483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1522,7 +1506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1549,7 +1533,7 @@
       </c>
       <c r="J26" s="5"/>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1572,7 +1556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1595,7 +1579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1618,7 +1602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1641,7 +1625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1664,7 +1648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1687,7 +1671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1710,7 +1694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1733,7 +1717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1756,7 +1740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1779,7 +1763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1802,7 +1786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1825,7 +1809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1852,7 +1836,7 @@
       </c>
       <c r="J39" s="5"/>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1879,7 +1863,7 @@
       </c>
       <c r="J40" s="5"/>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1905,7 +1889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1928,7 +1912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1951,7 +1935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1974,7 +1958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1997,7 +1981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2020,7 +2004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2046,7 +2030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2073,7 +2057,7 @@
       </c>
       <c r="J48" s="5"/>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2096,7 +2080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2119,7 +2103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2146,7 +2130,7 @@
       </c>
       <c r="J51" s="5"/>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2169,7 +2153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2192,7 +2176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2215,7 +2199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2238,7 +2222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2261,7 +2245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2284,7 +2268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2307,7 +2291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2337,7 +2321,7 @@
       </c>
       <c r="J59" s="5"/>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2360,7 +2344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2383,7 +2367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2410,7 +2394,7 @@
       </c>
       <c r="J62" s="5"/>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2433,7 +2417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2463,7 +2447,7 @@
       </c>
       <c r="J64" s="5"/>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2486,7 +2470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2509,7 +2493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2560,7 +2544,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2583,7 +2567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2606,7 +2590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2629,7 +2613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2652,7 +2636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2675,7 +2659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2698,7 +2682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2717,11 +2701,9 @@
       <c r="I75" s="5">
         <v>1</v>
       </c>
-      <c r="J75" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J75" s="5"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2744,7 +2726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2767,7 +2749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2790,7 +2772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2813,7 +2795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2832,11 +2814,9 @@
       <c r="I80" s="5">
         <v>1</v>
       </c>
-      <c r="J80" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J80" s="5"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2855,11 +2835,9 @@
       <c r="I81" s="5">
         <v>1</v>
       </c>
-      <c r="J81" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J81" s="5"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2882,7 +2860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2905,7 +2883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2928,7 +2906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2954,7 +2932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2977,7 +2955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3000,7 +2978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3027,7 +3005,7 @@
       </c>
       <c r="J88" s="5"/>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3078,7 +3056,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3101,7 +3079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3124,7 +3102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3147,7 +3125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3170,7 +3148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3193,7 +3171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3216,7 +3194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3239,7 +3217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3262,7 +3240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3285,7 +3263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3308,7 +3286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3331,7 +3309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -3354,7 +3332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -3377,7 +3355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -3400,7 +3378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -3423,7 +3401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -3446,7 +3424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -3465,11 +3443,9 @@
       <c r="I107" s="5">
         <v>1</v>
       </c>
-      <c r="J107" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J107" s="5"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -3492,7 +3468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -3515,7 +3491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -3538,7 +3514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -3557,11 +3533,9 @@
       <c r="I111" s="5">
         <v>1</v>
       </c>
-      <c r="J111" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J111" s="5"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -3584,7 +3558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -3607,7 +3581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -3630,7 +3604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -3660,7 +3634,7 @@
       </c>
       <c r="J115" s="5"/>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -3683,7 +3657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -3706,7 +3680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -3725,11 +3699,9 @@
       <c r="I118" s="5">
         <v>1</v>
       </c>
-      <c r="J118" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J118" s="5"/>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -3752,7 +3724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -3775,7 +3747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -3798,7 +3770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -3821,7 +3793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -3844,7 +3816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -3867,7 +3839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -3890,7 +3862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -3913,7 +3885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -3936,7 +3908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -3959,7 +3931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -3982,7 +3954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -4005,7 +3977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -4031,7 +4003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -4054,7 +4026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -4077,7 +4049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -4100,7 +4072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -4123,7 +4095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -4142,11 +4114,9 @@
       <c r="I136" s="5">
         <v>1</v>
       </c>
-      <c r="J136" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J136" s="5"/>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -4165,11 +4135,9 @@
       <c r="I137" s="5">
         <v>1</v>
       </c>
-      <c r="J137" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J137" s="5"/>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -4196,7 +4164,7 @@
       </c>
       <c r="J138" s="5"/>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -4222,7 +4190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -4270,10 +4238,10 @@
       <c r="H141" s="8"/>
       <c r="I141" s="8"/>
       <c r="J141" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -4296,7 +4264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -4319,7 +4287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -4342,7 +4310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -4365,7 +4333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -4388,7 +4356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -4411,7 +4379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -4434,7 +4402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -4485,7 +4453,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -4508,7 +4476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -4531,7 +4499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -4554,7 +4522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -4577,7 +4545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -4600,7 +4568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -4623,7 +4591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -4646,7 +4614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -4669,7 +4637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -4692,7 +4660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -4715,7 +4683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -4742,7 +4710,7 @@
       </c>
       <c r="J161" s="5"/>
     </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -4765,7 +4733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -4791,7 +4759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -4814,7 +4782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -4837,7 +4805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -4860,7 +4828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -4887,7 +4855,7 @@
       </c>
       <c r="J167" s="5"/>
     </row>
-    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -4914,7 +4882,7 @@
       </c>
       <c r="J168" s="5"/>
     </row>
-    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -4937,7 +4905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -4960,7 +4928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -4983,7 +4951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -5006,7 +4974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -5029,7 +4997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -5052,7 +5020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -5075,7 +5043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -5098,7 +5066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -5121,7 +5089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -5144,7 +5112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -5167,7 +5135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -5190,7 +5158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -5213,7 +5181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -5236,7 +5204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -5263,7 +5231,7 @@
       </c>
       <c r="J183" s="5"/>
     </row>
-    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -5286,7 +5254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -5309,7 +5277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -5332,7 +5300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -5355,7 +5323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -5381,7 +5349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -5411,7 +5379,7 @@
       </c>
       <c r="J189" s="5"/>
     </row>
-    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -5462,7 +5430,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -5481,11 +5449,9 @@
       <c r="I192" s="5">
         <v>1</v>
       </c>
-      <c r="J192" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J192" s="5"/>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -5508,7 +5474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -5531,7 +5497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -5554,7 +5520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -5577,7 +5543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -5600,7 +5566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -5623,7 +5589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -5646,7 +5612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -5669,7 +5635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -5692,7 +5658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -5715,7 +5681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -5738,7 +5704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -5761,7 +5727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -5784,7 +5750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -5807,7 +5773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -5830,7 +5796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -5857,7 +5823,7 @@
       </c>
       <c r="J208" s="5"/>
     </row>
-    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -5880,7 +5846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -5903,7 +5869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -5926,7 +5892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -5953,7 +5919,7 @@
       </c>
       <c r="J212" s="5"/>
     </row>
-    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -5976,7 +5942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -5999,7 +5965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -6029,7 +5995,7 @@
       </c>
       <c r="J215" s="5"/>
     </row>
-    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -6052,7 +6018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -6075,7 +6041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -6098,7 +6064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -6121,7 +6087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -6140,11 +6106,9 @@
       <c r="I220" s="5">
         <v>1</v>
       </c>
-      <c r="J220" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J220" s="5"/>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -6174,7 +6138,7 @@
       </c>
       <c r="J221" s="5"/>
     </row>
-    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -6197,7 +6161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -6214,7 +6178,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -6262,10 +6226,10 @@
       <c r="H225" s="8"/>
       <c r="I225" s="8"/>
       <c r="J225" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -6291,7 +6255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -6314,7 +6278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -6337,7 +6301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -6360,7 +6324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -6383,7 +6347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -6410,7 +6374,7 @@
       </c>
       <c r="J231" s="5"/>
     </row>
-    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -6433,7 +6397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -6479,10 +6443,10 @@
       <c r="H234" s="8"/>
       <c r="I234" s="8"/>
       <c r="J234" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -6508,7 +6472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -6531,7 +6495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -6554,7 +6518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -6577,7 +6541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -6600,7 +6564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -6623,7 +6587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -6649,7 +6613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -6704,7 +6668,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -6727,7 +6691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -6750,7 +6714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
@@ -6773,7 +6737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
@@ -6796,7 +6760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
@@ -6819,7 +6783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
@@ -6842,7 +6806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
@@ -6865,7 +6829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
@@ -6895,7 +6859,7 @@
       </c>
       <c r="J251" s="5"/>
     </row>
-    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
@@ -6925,7 +6889,7 @@
       </c>
       <c r="J252" s="5"/>
     </row>
-    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -6948,7 +6912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -6962,7 +6926,7 @@
         <v>7</v>
       </c>
       <c r="E254" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F254">
         <v>2026</v>
@@ -6971,7 +6935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -6994,7 +6958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -7017,7 +6981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -7040,7 +7004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -7063,7 +7027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -7086,7 +7050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -7109,7 +7073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -7132,7 +7096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -7155,7 +7119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
@@ -7206,7 +7170,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -7257,7 +7221,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -7280,7 +7244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
@@ -7303,7 +7267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -7326,7 +7290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -7349,7 +7313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -7375,7 +7339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -7394,11 +7358,9 @@
       <c r="I272" s="5">
         <v>1</v>
       </c>
-      <c r="J272" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J272" s="5"/>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
@@ -7421,7 +7383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -7444,7 +7406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
@@ -7474,7 +7436,7 @@
       </c>
       <c r="J275" s="5"/>
     </row>
-    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
@@ -7497,7 +7459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
@@ -7524,7 +7486,7 @@
       </c>
       <c r="J277" s="5"/>
     </row>
-    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>277</v>
       </c>
@@ -7547,7 +7509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
@@ -7570,7 +7532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
@@ -7593,7 +7555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
@@ -7616,7 +7578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
@@ -7639,7 +7601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>282</v>
       </c>
@@ -7662,7 +7624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>283</v>
       </c>
@@ -7685,7 +7647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>284</v>
       </c>
@@ -7708,7 +7670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>285</v>
       </c>
@@ -7731,7 +7693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>286</v>
       </c>
@@ -7754,7 +7716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>287</v>
       </c>
@@ -7777,7 +7739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>288</v>
       </c>
@@ -7800,7 +7762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>289</v>
       </c>
@@ -7823,7 +7785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>290</v>
       </c>
@@ -7850,7 +7812,7 @@
       </c>
       <c r="J291" s="5"/>
     </row>
-    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>291</v>
       </c>
@@ -7869,11 +7831,9 @@
       <c r="I292" s="5">
         <v>1</v>
       </c>
-      <c r="J292" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J292" s="5"/>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>292</v>
       </c>
@@ -7896,7 +7856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>293</v>
       </c>
@@ -7919,7 +7879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>294</v>
       </c>
@@ -7942,7 +7902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>295</v>
       </c>
@@ -7965,7 +7925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>296</v>
       </c>
@@ -8018,7 +7978,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="299" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>298</v>
       </c>
@@ -8048,7 +8008,7 @@
       </c>
       <c r="J299" s="5"/>
     </row>
-    <row r="300" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>299</v>
       </c>
@@ -8071,7 +8031,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>300</v>
       </c>
@@ -8094,7 +8054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>301</v>
       </c>
@@ -8117,7 +8077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>302</v>
       </c>
@@ -8140,7 +8100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>303</v>
       </c>
@@ -8163,7 +8123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>304</v>
       </c>
@@ -8186,7 +8146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>305</v>
       </c>
@@ -8209,7 +8169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>306</v>
       </c>
@@ -8232,7 +8192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>307</v>
       </c>
@@ -8255,7 +8215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>308</v>
       </c>
@@ -8278,7 +8238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>309</v>
       </c>
@@ -8301,7 +8261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>310</v>
       </c>
@@ -8324,7 +8284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>311</v>
       </c>
@@ -8347,7 +8307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>312</v>
       </c>
@@ -8370,7 +8330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>313</v>
       </c>
@@ -8393,7 +8353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>314</v>
       </c>
@@ -8416,7 +8376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>315</v>
       </c>
@@ -8439,7 +8399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>316</v>
       </c>
@@ -8462,7 +8422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>317</v>
       </c>
@@ -8485,7 +8445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>318</v>
       </c>
@@ -8508,7 +8468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>319</v>
       </c>
@@ -8534,7 +8494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>320</v>
       </c>
@@ -8561,7 +8521,7 @@
       </c>
       <c r="J321" s="5"/>
     </row>
-    <row r="322" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>321</v>
       </c>
@@ -8587,7 +8547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>322</v>
       </c>
@@ -8610,7 +8570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>323</v>
       </c>
@@ -8633,7 +8593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>324</v>
       </c>
@@ -8656,7 +8616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>325</v>
       </c>
@@ -8679,7 +8639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>326</v>
       </c>
@@ -8706,7 +8666,7 @@
       </c>
       <c r="J327" s="5"/>
     </row>
-    <row r="328" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>327</v>
       </c>
@@ -8729,7 +8689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>328</v>
       </c>
@@ -8759,7 +8719,7 @@
       </c>
       <c r="J329" s="5"/>
     </row>
-    <row r="330" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>329</v>
       </c>
@@ -8782,7 +8742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>330</v>
       </c>
@@ -8805,7 +8765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>331</v>
       </c>
@@ -8828,7 +8788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>332</v>
       </c>
@@ -8876,10 +8836,10 @@
       <c r="H334" s="8"/>
       <c r="I334" s="8"/>
       <c r="J334" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="335" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>334</v>
       </c>
@@ -8902,7 +8862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>335</v>
       </c>
@@ -8925,7 +8885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>336</v>
       </c>
@@ -8948,7 +8908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>337</v>
       </c>
@@ -8971,7 +8931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>338</v>
       </c>
@@ -9022,7 +8982,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="341" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>340</v>
       </c>
@@ -9075,7 +9035,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="343" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>342</v>
       </c>
@@ -9102,7 +9062,7 @@
       </c>
       <c r="J343" s="5"/>
     </row>
-    <row r="344" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>343</v>
       </c>
@@ -9125,7 +9085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>344</v>
       </c>
@@ -9148,7 +9108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>345</v>
       </c>
@@ -9227,7 +9187,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="349" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>348</v>
       </c>
@@ -9257,7 +9217,7 @@
       </c>
       <c r="J349" s="5"/>
     </row>
-    <row r="350" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>349</v>
       </c>
@@ -9280,7 +9240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="351" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>350</v>
       </c>
@@ -9303,7 +9263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>351</v>
       </c>
@@ -9326,7 +9286,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="353" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>352</v>
       </c>
@@ -9349,7 +9309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>353</v>
       </c>
@@ -9372,7 +9332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>354</v>
       </c>
@@ -9395,7 +9355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>355</v>
       </c>
@@ -9418,7 +9378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>356</v>
       </c>
@@ -9441,7 +9401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>357</v>
       </c>
@@ -9464,7 +9424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>358</v>
       </c>
@@ -9487,7 +9447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>359</v>
       </c>
@@ -9510,7 +9470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>360</v>
       </c>
@@ -9533,7 +9493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>361</v>
       </c>
@@ -9556,7 +9516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>362</v>
       </c>
@@ -9579,7 +9539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>363</v>
       </c>
@@ -9602,7 +9562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>364</v>
       </c>
@@ -9621,11 +9581,9 @@
       <c r="I365" s="5">
         <v>1</v>
       </c>
-      <c r="J365" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J365" s="5"/>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>365</v>
       </c>
@@ -9648,7 +9606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>366</v>
       </c>
@@ -9671,7 +9629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>367</v>
       </c>
@@ -9698,7 +9656,7 @@
       </c>
       <c r="J368" s="5"/>
     </row>
-    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>368</v>
       </c>
@@ -9721,7 +9679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>369</v>
       </c>
@@ -9744,7 +9702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>370</v>
       </c>
@@ -9767,7 +9725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>371</v>
       </c>
@@ -9784,7 +9742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="373" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>372</v>
       </c>
@@ -9807,7 +9765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>373</v>
       </c>
@@ -9852,7 +9810,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="376" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>375</v>
       </c>
@@ -9882,7 +9840,7 @@
       </c>
       <c r="J376" s="5"/>
     </row>
-    <row r="377" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>376</v>
       </c>
@@ -9905,7 +9863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="378" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>377</v>
       </c>
@@ -9928,7 +9886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>378</v>
       </c>
@@ -9951,7 +9909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>379</v>
       </c>
@@ -9981,7 +9939,7 @@
       </c>
       <c r="J380" s="5"/>
     </row>
-    <row r="381" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>380</v>
       </c>
@@ -10004,7 +9962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>381</v>
       </c>
@@ -10027,7 +9985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>382</v>
       </c>
@@ -10050,7 +10008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>383</v>
       </c>
@@ -10073,7 +10031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>384</v>
       </c>
@@ -10096,7 +10054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>385</v>
       </c>
@@ -10119,7 +10077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>386</v>
       </c>
@@ -10142,7 +10100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>387</v>
       </c>
@@ -10165,7 +10123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>388</v>
       </c>
@@ -10188,7 +10146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>389</v>
       </c>
@@ -10211,7 +10169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>390</v>
       </c>
@@ -10234,7 +10192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>391</v>
       </c>
@@ -10257,7 +10215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>392</v>
       </c>
@@ -10276,11 +10234,9 @@
       <c r="I393" s="5">
         <v>1</v>
       </c>
-      <c r="J393" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="394" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J393" s="5"/>
+    </row>
+    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>393</v>
       </c>
@@ -10303,7 +10259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>394</v>
       </c>
@@ -10326,7 +10282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>395</v>
       </c>
@@ -10349,7 +10305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>396</v>
       </c>
@@ -10372,7 +10328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>397</v>
       </c>
@@ -10395,7 +10351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>398</v>
       </c>
@@ -10418,7 +10374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="400" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>399</v>
       </c>
@@ -10444,7 +10400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>400</v>
       </c>
@@ -10474,7 +10430,7 @@
       </c>
       <c r="J401" s="5"/>
     </row>
-    <row r="402" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>401</v>
       </c>
@@ -10497,7 +10453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="403" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>402</v>
       </c>
@@ -10554,7 +10510,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="405" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>404</v>
       </c>
@@ -10577,7 +10533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>405</v>
       </c>
@@ -10600,7 +10556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>406</v>
       </c>
@@ -10623,7 +10579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>407</v>
       </c>
@@ -10646,7 +10602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>408</v>
       </c>
@@ -10669,7 +10625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>409</v>
       </c>
@@ -10692,7 +10648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>410</v>
       </c>
@@ -10715,7 +10671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>411</v>
       </c>
@@ -10738,7 +10694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>412</v>
       </c>
@@ -10761,7 +10717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>413</v>
       </c>
@@ -10784,7 +10740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>414</v>
       </c>
@@ -10807,7 +10763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>415</v>
       </c>
@@ -10830,7 +10786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>416</v>
       </c>
@@ -10853,7 +10809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>417</v>
       </c>
@@ -10876,7 +10832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>418</v>
       </c>
@@ -10899,7 +10855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>419</v>
       </c>
@@ -10922,7 +10878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>420</v>
       </c>
@@ -10945,7 +10901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>421</v>
       </c>
@@ -10968,7 +10924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>422</v>
       </c>
@@ -10998,7 +10954,7 @@
       </c>
       <c r="J423" s="5"/>
     </row>
-    <row r="424" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>423</v>
       </c>
@@ -11021,7 +10977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>424</v>
       </c>
@@ -11044,7 +11000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>425</v>
       </c>
@@ -11095,7 +11051,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="428" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>427</v>
       </c>
@@ -11118,7 +11074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>428</v>
       </c>
@@ -11145,7 +11101,7 @@
       </c>
       <c r="J429" s="5"/>
     </row>
-    <row r="430" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>429</v>
       </c>
@@ -11168,7 +11124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="431" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>430</v>
       </c>
@@ -11191,7 +11147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="432" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>431</v>
       </c>
@@ -11214,7 +11170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>432</v>
       </c>
@@ -11237,7 +11193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>433</v>
       </c>
@@ -11260,7 +11216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>434</v>
       </c>
@@ -11283,7 +11239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>435</v>
       </c>
@@ -11306,7 +11262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>436</v>
       </c>
@@ -11329,7 +11285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>437</v>
       </c>
@@ -11352,7 +11308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>438</v>
       </c>
@@ -11375,7 +11331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>439</v>
       </c>
@@ -11398,7 +11354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>440</v>
       </c>
@@ -11428,7 +11384,7 @@
       </c>
       <c r="J441" s="5"/>
     </row>
-    <row r="442" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>441</v>
       </c>
@@ -11455,7 +11411,7 @@
       </c>
       <c r="J442" s="5"/>
     </row>
-    <row r="443" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>442</v>
       </c>
@@ -11478,7 +11434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>443</v>
       </c>
@@ -11501,7 +11457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>444</v>
       </c>
@@ -11524,7 +11480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>445</v>
       </c>
@@ -11547,7 +11503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>446</v>
       </c>
@@ -11570,7 +11526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>447</v>
       </c>
@@ -11593,7 +11549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>448</v>
       </c>
@@ -11620,7 +11576,7 @@
       </c>
       <c r="J449" s="5"/>
     </row>
-    <row r="450" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>449</v>
       </c>
@@ -11643,7 +11599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>450</v>
       </c>
@@ -11666,7 +11622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="452" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>451</v>
       </c>
@@ -11689,7 +11645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="453" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>452</v>
       </c>
@@ -11712,7 +11668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="454" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>453</v>
       </c>
@@ -11735,7 +11691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>454</v>
       </c>
@@ -11758,7 +11714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>455</v>
       </c>
@@ -11781,7 +11737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>456</v>
       </c>
@@ -11804,7 +11760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>457</v>
       </c>
@@ -11827,7 +11783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>458</v>
       </c>
@@ -11850,7 +11806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>459</v>
       </c>
@@ -11873,7 +11829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="461" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>460</v>
       </c>
@@ -11896,7 +11852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="462" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>461</v>
       </c>
@@ -11919,7 +11875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>462</v>
       </c>
@@ -11942,7 +11898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>463</v>
       </c>
@@ -11965,7 +11921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>464</v>
       </c>
@@ -11988,7 +11944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>465</v>
       </c>
@@ -12011,7 +11967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>466</v>
       </c>
@@ -12034,7 +11990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>467</v>
       </c>
@@ -12057,7 +12013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="469" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>468</v>
       </c>
@@ -12080,7 +12036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>469</v>
       </c>
@@ -12103,7 +12059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>470</v>
       </c>
@@ -12126,7 +12082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="472" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>471</v>
       </c>
@@ -12149,7 +12105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>472</v>
       </c>
@@ -12172,7 +12128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>473</v>
       </c>
@@ -12202,7 +12158,7 @@
       </c>
       <c r="J474" s="5"/>
     </row>
-    <row r="475" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>474</v>
       </c>
@@ -12229,7 +12185,7 @@
       </c>
       <c r="J475" s="5"/>
     </row>
-    <row r="476" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>475</v>
       </c>
@@ -12252,7 +12208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>476</v>
       </c>
@@ -12275,7 +12231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="478" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>477</v>
       </c>
@@ -12298,7 +12254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>478</v>
       </c>
@@ -12317,11 +12273,9 @@
       <c r="I479" s="5">
         <v>1</v>
       </c>
-      <c r="J479" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="480" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J479" s="5"/>
+    </row>
+    <row r="480" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>479</v>
       </c>
@@ -12344,7 +12298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>480</v>
       </c>
@@ -12367,7 +12321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>481</v>
       </c>
@@ -12390,7 +12344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>482</v>
       </c>
@@ -12413,7 +12367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="484" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>483</v>
       </c>
@@ -12436,7 +12390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>484</v>
       </c>
@@ -12459,7 +12413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>485</v>
       </c>
@@ -12482,7 +12436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="487" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>486</v>
       </c>
@@ -12505,7 +12459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>487</v>
       </c>
@@ -12528,7 +12482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>488</v>
       </c>
@@ -12551,7 +12505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>489</v>
       </c>
@@ -12574,7 +12528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>490</v>
       </c>
@@ -12597,7 +12551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="492" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>491</v>
       </c>
@@ -12620,7 +12574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="493" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>492</v>
       </c>
@@ -12639,11 +12593,9 @@
       <c r="I493" s="5">
         <v>1</v>
       </c>
-      <c r="J493" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="494" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J493" s="5"/>
+    </row>
+    <row r="494" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>493</v>
       </c>
@@ -12666,7 +12618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>494</v>
       </c>
@@ -12689,7 +12641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="496" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>495</v>
       </c>
@@ -12712,7 +12664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="497" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>496</v>
       </c>
@@ -12735,7 +12687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="498" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>497</v>
       </c>
@@ -12761,7 +12713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="499" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>498</v>
       </c>
@@ -12819,7 +12771,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="501" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>500</v>
       </c>
@@ -12838,11 +12790,9 @@
       <c r="I501" s="5">
         <v>1</v>
       </c>
-      <c r="J501" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="502" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J501" s="5"/>
+    </row>
+    <row r="502" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>501</v>
       </c>
@@ -12865,7 +12815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>502</v>
       </c>
@@ -12918,7 +12868,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="505" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>504</v>
       </c>
@@ -12944,7 +12894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>505</v>
       </c>
@@ -12967,7 +12917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="507" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>506</v>
       </c>
@@ -12990,7 +12940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>507</v>
       </c>
@@ -13013,7 +12963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>508</v>
       </c>
@@ -13036,7 +12986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>509</v>
       </c>
@@ -13066,7 +13016,7 @@
       </c>
       <c r="J510" s="5"/>
     </row>
-    <row r="511" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>510</v>
       </c>
@@ -13089,7 +13039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>511</v>
       </c>
@@ -13116,7 +13066,7 @@
       </c>
       <c r="J512" s="5"/>
     </row>
-    <row r="513" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>512</v>
       </c>
@@ -13139,7 +13089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>513</v>
       </c>
@@ -13162,7 +13112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="515" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>514</v>
       </c>
@@ -13185,7 +13135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>515</v>
       </c>
@@ -13208,7 +13158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="517" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>516</v>
       </c>
@@ -13231,7 +13181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>517</v>
       </c>
@@ -13259,7 +13209,7 @@
       <c r="I518" s="5"/>
       <c r="J518" s="5"/>
     </row>
-    <row r="519" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>518</v>
       </c>
@@ -13282,7 +13232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>519</v>
       </c>
@@ -13305,7 +13255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>520</v>
       </c>
@@ -13328,7 +13278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>521</v>
       </c>
@@ -13351,7 +13301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>522</v>
       </c>
@@ -13374,7 +13324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>523</v>
       </c>
@@ -13401,7 +13351,7 @@
       </c>
       <c r="J524" s="5"/>
     </row>
-    <row r="525" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>524</v>
       </c>
@@ -13427,7 +13377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="526" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>525</v>
       </c>
@@ -13450,7 +13400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>526</v>
       </c>
@@ -13473,7 +13423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>527</v>
       </c>
@@ -13496,7 +13446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>528</v>
       </c>
@@ -13547,7 +13497,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="531" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>530</v>
       </c>
@@ -13570,7 +13520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>531</v>
       </c>
@@ -13649,7 +13599,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="535" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>534</v>
       </c>
@@ -13700,7 +13650,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="537" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>536</v>
       </c>
@@ -13751,7 +13701,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="539" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>538</v>
       </c>
@@ -13774,7 +13724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>539</v>
       </c>
@@ -13797,7 +13747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>540</v>
       </c>
@@ -13816,11 +13766,9 @@
       <c r="I541" s="5">
         <v>1</v>
       </c>
-      <c r="J541" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="542" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J541" s="5"/>
+    </row>
+    <row r="542" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>541</v>
       </c>
@@ -13850,7 +13798,7 @@
       </c>
       <c r="J542" s="5"/>
     </row>
-    <row r="543" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>542</v>
       </c>
@@ -13873,7 +13821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>543</v>
       </c>
@@ -13896,7 +13844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>544</v>
       </c>
@@ -13951,7 +13899,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="547" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>546</v>
       </c>
@@ -13974,7 +13922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>547</v>
       </c>
@@ -14004,7 +13952,7 @@
       </c>
       <c r="J548" s="5"/>
     </row>
-    <row r="549" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>548</v>
       </c>
@@ -14027,7 +13975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>549</v>
       </c>
@@ -14050,7 +13998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="551" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>550</v>
       </c>
@@ -14069,11 +14017,9 @@
       <c r="I551" s="5">
         <v>1</v>
       </c>
-      <c r="J551" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="552" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J551" s="5"/>
+    </row>
+    <row r="552" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>551</v>
       </c>
@@ -14096,7 +14042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="553" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>552</v>
       </c>
@@ -14119,7 +14065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="554" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>553</v>
       </c>
@@ -14138,11 +14084,9 @@
       <c r="I554" s="5">
         <v>1</v>
       </c>
-      <c r="J554" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="555" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J554" s="5"/>
+    </row>
+    <row r="555" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>554</v>
       </c>
@@ -14165,7 +14109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="556" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>555</v>
       </c>
@@ -14188,7 +14132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="557" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>556</v>
       </c>
@@ -14241,7 +14185,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="559" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>558</v>
       </c>
@@ -14264,7 +14208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="560" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>559</v>
       </c>
@@ -14294,7 +14238,7 @@
       </c>
       <c r="J560" s="5"/>
     </row>
-    <row r="561" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>560</v>
       </c>
@@ -14317,7 +14261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="562" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>561</v>
       </c>
@@ -14344,7 +14288,7 @@
       </c>
       <c r="J562" s="5"/>
     </row>
-    <row r="563" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>562</v>
       </c>
@@ -14395,7 +14339,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="565" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>564</v>
       </c>
@@ -14414,11 +14358,9 @@
       <c r="I565" s="5">
         <v>1</v>
       </c>
-      <c r="J565" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="566" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J565" s="5"/>
+    </row>
+    <row r="566" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>565</v>
       </c>
@@ -14445,7 +14387,7 @@
       </c>
       <c r="J566" s="5"/>
     </row>
-    <row r="567" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>566</v>
       </c>
@@ -14468,7 +14410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="568" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>567</v>
       </c>
@@ -14491,7 +14433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="569" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>568</v>
       </c>
@@ -14510,11 +14452,9 @@
       <c r="I569" s="5">
         <v>1</v>
       </c>
-      <c r="J569" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="570" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J569" s="5"/>
+    </row>
+    <row r="570" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>569</v>
       </c>
@@ -14537,7 +14477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="571" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>570</v>
       </c>
@@ -14560,7 +14500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="572" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>571</v>
       </c>
@@ -14583,7 +14523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="573" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>572</v>
       </c>
@@ -14606,7 +14546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="574" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>573</v>
       </c>
@@ -14629,7 +14569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>574</v>
       </c>
@@ -14652,7 +14592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="576" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>575</v>
       </c>
@@ -14679,7 +14619,7 @@
       </c>
       <c r="J576" s="5"/>
     </row>
-    <row r="577" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>576</v>
       </c>
@@ -14702,7 +14642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="578" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>577</v>
       </c>
@@ -14729,7 +14669,7 @@
       </c>
       <c r="J578" s="5"/>
     </row>
-    <row r="579" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>578</v>
       </c>
@@ -14752,7 +14692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="580" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>579</v>
       </c>
@@ -14775,7 +14715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="581" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>580</v>
       </c>
@@ -14826,7 +14766,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="583" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>582</v>
       </c>
@@ -14849,7 +14789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="584" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>583</v>
       </c>
@@ -14872,7 +14812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="585" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>584</v>
       </c>
@@ -14895,7 +14835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="586" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>585</v>
       </c>
@@ -14918,7 +14858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="587" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>586</v>
       </c>
@@ -14941,7 +14881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>587</v>
       </c>
@@ -14964,7 +14904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="589" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>588</v>
       </c>
@@ -14987,7 +14927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="590" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>589</v>
       </c>
@@ -15010,7 +14950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="591" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>590</v>
       </c>
@@ -15029,11 +14969,9 @@
       <c r="I591" s="5">
         <v>1</v>
       </c>
-      <c r="J591" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="592" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J591" s="5"/>
+    </row>
+    <row r="592" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>591</v>
       </c>
@@ -15056,7 +14994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="593" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>592</v>
       </c>
@@ -15079,7 +15017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="594" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>593</v>
       </c>
@@ -15132,7 +15070,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="596" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>595</v>
       </c>
@@ -15159,7 +15097,7 @@
       </c>
       <c r="J596" s="5"/>
     </row>
-    <row r="597" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>596</v>
       </c>
@@ -15185,7 +15123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="598" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>597</v>
       </c>
@@ -15208,7 +15146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="599" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>598</v>
       </c>
@@ -15234,7 +15172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="600" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>599</v>
       </c>
@@ -15257,7 +15195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="601" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>600</v>
       </c>
@@ -15280,7 +15218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="602" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>601</v>
       </c>
@@ -15303,7 +15241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="603" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>602</v>
       </c>
@@ -15333,7 +15271,7 @@
       </c>
       <c r="J603" s="5"/>
     </row>
-    <row r="604" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>603</v>
       </c>
@@ -15356,7 +15294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="605" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>604</v>
       </c>
@@ -15379,7 +15317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="606" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>605</v>
       </c>
@@ -15402,7 +15340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="607" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>606</v>
       </c>
@@ -15425,7 +15363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="608" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A608">
         <v>607</v>
       </c>
@@ -15448,7 +15386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="609" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>608</v>
       </c>
@@ -15471,7 +15409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="610" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>609</v>
       </c>
@@ -15494,7 +15432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="611" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>610</v>
       </c>
@@ -15517,7 +15455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="612" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A612">
         <v>611</v>
       </c>
@@ -15540,7 +15478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="613" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>612</v>
       </c>
@@ -15563,7 +15501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="614" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A614">
         <v>613</v>
       </c>
@@ -15586,7 +15524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="615" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>614</v>
       </c>
@@ -15609,7 +15547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="616" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A616">
         <v>615</v>
       </c>
@@ -15632,7 +15570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="617" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>616</v>
       </c>
@@ -15655,7 +15593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="618" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A618">
         <v>617</v>
       </c>
@@ -15678,7 +15616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="619" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>618</v>
       </c>
@@ -15704,7 +15642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="620" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A620">
         <v>619</v>
       </c>
@@ -15723,11 +15661,9 @@
       <c r="I620" s="5">
         <v>1</v>
       </c>
-      <c r="J620" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="621" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J620" s="5"/>
+    </row>
+    <row r="621" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>620</v>
       </c>
@@ -15754,7 +15690,7 @@
       </c>
       <c r="J621" s="5"/>
     </row>
-    <row r="622" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A622">
         <v>621</v>
       </c>
@@ -15777,7 +15713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="623" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>622</v>
       </c>
@@ -15800,7 +15736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="624" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A624">
         <v>623</v>
       </c>
@@ -15823,7 +15759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="625" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>624</v>
       </c>
@@ -15846,7 +15782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="626" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>625</v>
       </c>
@@ -15897,7 +15833,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="628" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A628">
         <v>627</v>
       </c>
@@ -15920,7 +15856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="629" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>628</v>
       </c>
@@ -15943,7 +15879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="630" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>629</v>
       </c>
@@ -15966,7 +15902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="631" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>630</v>
       </c>
@@ -15989,7 +15925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="632" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A632">
         <v>631</v>
       </c>
@@ -16040,7 +15976,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="634" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A634">
         <v>633</v>
       </c>
@@ -16063,7 +15999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="635" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A635">
         <v>634</v>
       </c>
@@ -16086,7 +16022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="636" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A636">
         <v>635</v>
       </c>
@@ -16109,10 +16045,10 @@
         <v>1</v>
       </c>
       <c r="J636" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="637" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="637" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A637">
         <v>636</v>
       </c>
@@ -16135,7 +16071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="638" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A638">
         <v>637</v>
       </c>
@@ -16158,7 +16094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="639" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>638</v>
       </c>
@@ -16181,7 +16117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="640" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A640">
         <v>639</v>
       </c>
@@ -16204,7 +16140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="641" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A641">
         <v>640</v>
       </c>
@@ -16227,7 +16163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="642" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A642">
         <v>641</v>
       </c>
@@ -16250,7 +16186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="643" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A643">
         <v>642</v>
       </c>
@@ -16273,7 +16209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="644" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A644">
         <v>643</v>
       </c>
@@ -16296,7 +16232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="645" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A645">
         <v>644</v>
       </c>
@@ -16319,7 +16255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="646" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A646">
         <v>645</v>
       </c>
@@ -16349,7 +16285,7 @@
       </c>
       <c r="J646" s="5"/>
     </row>
-    <row r="647" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A647">
         <v>646</v>
       </c>
@@ -16368,11 +16304,9 @@
       <c r="I647" s="5">
         <v>1</v>
       </c>
-      <c r="J647" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="648" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J647" s="5"/>
+    </row>
+    <row r="648" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A648">
         <v>647</v>
       </c>
@@ -16395,7 +16329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="649" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A649">
         <v>648</v>
       </c>
@@ -16418,7 +16352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="650" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A650">
         <v>649</v>
       </c>
@@ -16441,7 +16375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="651" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A651">
         <v>650</v>
       </c>
@@ -16471,7 +16405,7 @@
       </c>
       <c r="J651" s="5"/>
     </row>
-    <row r="652" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A652">
         <v>651</v>
       </c>
@@ -16498,7 +16432,7 @@
       </c>
       <c r="J652" s="5"/>
     </row>
-    <row r="653" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A653">
         <v>652</v>
       </c>
@@ -16521,7 +16455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="654" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A654">
         <v>653</v>
       </c>
@@ -16544,7 +16478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="655" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A655">
         <v>654</v>
       </c>
@@ -16567,7 +16501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="656" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A656">
         <v>655</v>
       </c>
@@ -16590,7 +16524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="657" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A657">
         <v>656</v>
       </c>
@@ -16641,7 +16575,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="659" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A659">
         <v>658</v>
       </c>
@@ -16664,7 +16598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="660" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A660">
         <v>659</v>
       </c>
@@ -16687,7 +16621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="661" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A661">
         <v>660</v>
       </c>
@@ -16710,7 +16644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="662" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A662">
         <v>661</v>
       </c>
@@ -16733,7 +16667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="663" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A663">
         <v>662</v>
       </c>
@@ -16784,7 +16718,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="665" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A665">
         <v>664</v>
       </c>
@@ -16807,7 +16741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="666" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A666">
         <v>665</v>
       </c>
@@ -16830,7 +16764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="667" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A667">
         <v>666</v>
       </c>
@@ -16853,7 +16787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="668" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A668">
         <v>667</v>
       </c>
@@ -16876,7 +16810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="669" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A669">
         <v>668</v>
       </c>
@@ -16899,7 +16833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="670" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A670">
         <v>669</v>
       </c>
@@ -16945,10 +16879,10 @@
       <c r="H671" s="8"/>
       <c r="I671" s="8"/>
       <c r="J671" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="672" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="672" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A672">
         <v>671</v>
       </c>
@@ -16975,7 +16909,7 @@
       </c>
       <c r="J672" s="5"/>
     </row>
-    <row r="673" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A673">
         <v>672</v>
       </c>
@@ -17002,7 +16936,7 @@
       </c>
       <c r="J673" s="5"/>
     </row>
-    <row r="674" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A674">
         <v>673</v>
       </c>
@@ -17053,7 +16987,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="676" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A676">
         <v>675</v>
       </c>
@@ -17076,7 +17010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="677" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A677">
         <v>676</v>
       </c>
@@ -17099,7 +17033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="678" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A678">
         <v>677</v>
       </c>
@@ -17126,7 +17060,7 @@
       </c>
       <c r="J678" s="5"/>
     </row>
-    <row r="679" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A679">
         <v>678</v>
       </c>
@@ -17149,7 +17083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="680" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A680">
         <v>679</v>
       </c>
@@ -17172,7 +17106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="681" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A681">
         <v>680</v>
       </c>
@@ -17199,7 +17133,7 @@
       </c>
       <c r="J681" s="5"/>
     </row>
-    <row r="682" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A682">
         <v>681</v>
       </c>
@@ -17222,7 +17156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="683" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A683">
         <v>682</v>
       </c>
@@ -17252,7 +17186,7 @@
       </c>
       <c r="J683" s="5"/>
     </row>
-    <row r="684" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A684">
         <v>683</v>
       </c>
@@ -17275,7 +17209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="685" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A685">
         <v>684</v>
       </c>
@@ -17298,7 +17232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="686" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A686">
         <v>685</v>
       </c>
@@ -17321,7 +17255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="687" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A687">
         <v>686</v>
       </c>
@@ -17344,7 +17278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="688" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A688">
         <v>687</v>
       </c>
@@ -17371,7 +17305,7 @@
       </c>
       <c r="J688" s="5"/>
     </row>
-    <row r="689" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A689">
         <v>688</v>
       </c>
@@ -17394,7 +17328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="690" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A690">
         <v>689</v>
       </c>
@@ -17417,7 +17351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="691" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A691">
         <v>690</v>
       </c>
@@ -17440,7 +17374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="692" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A692">
         <v>691</v>
       </c>
@@ -17463,7 +17397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="693" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A693">
         <v>692</v>
       </c>
@@ -17486,7 +17420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="694" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A694">
         <v>693</v>
       </c>
@@ -17509,7 +17443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="695" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A695">
         <v>694</v>
       </c>
@@ -17532,7 +17466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="696" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A696">
         <v>695</v>
       </c>
@@ -17555,7 +17489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="697" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A697">
         <v>696</v>
       </c>
@@ -17578,7 +17512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="698" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A698">
         <v>697</v>
       </c>
@@ -17601,7 +17535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="699" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A699">
         <v>698</v>
       </c>
@@ -17624,7 +17558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="700" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A700">
         <v>699</v>
       </c>
@@ -17647,7 +17581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="701" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A701">
         <v>700</v>
       </c>
@@ -17670,7 +17604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="702" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A702">
         <v>701</v>
       </c>
@@ -17693,7 +17627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="703" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A703">
         <v>702</v>
       </c>
@@ -17716,7 +17650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="704" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A704">
         <v>703</v>
       </c>
@@ -17739,7 +17673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="705" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A705">
         <v>704</v>
       </c>
@@ -17762,7 +17696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="706" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A706">
         <v>705</v>
       </c>
@@ -17785,7 +17719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="707" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A707">
         <v>706</v>
       </c>
@@ -17808,7 +17742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="708" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A708">
         <v>707</v>
       </c>
@@ -17831,7 +17765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="709" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A709">
         <v>708</v>
       </c>
@@ -17854,7 +17788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="710" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A710">
         <v>709</v>
       </c>
@@ -17877,7 +17811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="711" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A711">
         <v>710</v>
       </c>
@@ -17900,7 +17834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="712" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A712">
         <v>711</v>
       </c>
@@ -17926,7 +17860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="713" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A713">
         <v>712</v>
       </c>
@@ -17949,7 +17883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="714" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A714">
         <v>713</v>
       </c>
@@ -17972,7 +17906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="715" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A715">
         <v>714</v>
       </c>
@@ -17995,7 +17929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="716" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A716">
         <v>715</v>
       </c>
@@ -18018,7 +17952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="717" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A717">
         <v>716</v>
       </c>
@@ -18077,7 +18011,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="719" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A719">
         <v>718</v>
       </c>
@@ -18100,7 +18034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="720" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A720">
         <v>719</v>
       </c>
@@ -18130,7 +18064,7 @@
       </c>
       <c r="J720" s="5"/>
     </row>
-    <row r="721" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A721">
         <v>720</v>
       </c>
@@ -18153,7 +18087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="722" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A722">
         <v>721</v>
       </c>
@@ -18172,11 +18106,9 @@
       <c r="I722" s="5">
         <v>1</v>
       </c>
-      <c r="J722" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="723" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J722" s="5"/>
+    </row>
+    <row r="723" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A723">
         <v>722</v>
       </c>
@@ -18199,7 +18131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="724" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A724">
         <v>723</v>
       </c>
@@ -18222,7 +18154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="725" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A725">
         <v>724</v>
       </c>
@@ -18245,7 +18177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="726" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A726">
         <v>725</v>
       </c>
@@ -18268,7 +18200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="727" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A727">
         <v>726</v>
       </c>
@@ -18291,7 +18223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="728" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A728">
         <v>727</v>
       </c>
@@ -18314,7 +18246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="729" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A729">
         <v>728</v>
       </c>
@@ -18337,7 +18269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="730" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A730">
         <v>729</v>
       </c>
@@ -18360,7 +18292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="731" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A731">
         <v>730</v>
       </c>
@@ -18383,7 +18315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="732" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A732">
         <v>731</v>
       </c>
@@ -18406,7 +18338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="733" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A733">
         <v>732</v>
       </c>
@@ -18429,7 +18361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="734" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A734">
         <v>733</v>
       </c>
@@ -18452,7 +18384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="735" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A735">
         <v>734</v>
       </c>
@@ -18475,7 +18407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="736" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A736">
         <v>735</v>
       </c>
@@ -18498,7 +18430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="737" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A737">
         <v>736</v>
       </c>
@@ -18521,7 +18453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="738" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A738">
         <v>737</v>
       </c>
@@ -18544,7 +18476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="739" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A739">
         <v>738</v>
       </c>
@@ -18574,7 +18506,7 @@
       </c>
       <c r="J739" s="5"/>
     </row>
-    <row r="740" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A740">
         <v>739</v>
       </c>
@@ -18653,7 +18585,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="743" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A743">
         <v>742</v>
       </c>
@@ -18676,7 +18608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="744" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A744">
         <v>743</v>
       </c>
@@ -18703,7 +18635,7 @@
       </c>
       <c r="J744" s="5"/>
     </row>
-    <row r="745" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A745">
         <v>744</v>
       </c>
@@ -18726,7 +18658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="746" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A746">
         <v>745</v>
       </c>
@@ -18781,7 +18713,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="748" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A748">
         <v>747</v>
       </c>
@@ -18804,7 +18736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="749" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A749">
         <v>748</v>
       </c>
@@ -18827,7 +18759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="750" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A750">
         <v>749</v>
       </c>
@@ -18850,7 +18782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="751" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A751">
         <v>750</v>
       </c>
@@ -18864,16 +18796,14 @@
         <v>7</v>
       </c>
       <c r="E751" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I751" s="5">
         <v>1</v>
       </c>
-      <c r="J751" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="752" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J751" s="5"/>
+    </row>
+    <row r="752" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A752">
         <v>751</v>
       </c>
@@ -18896,7 +18826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="753" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A753">
         <v>752</v>
       </c>
@@ -18919,7 +18849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="754" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A754">
         <v>753</v>
       </c>
@@ -18942,7 +18872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="755" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A755">
         <v>754</v>
       </c>
@@ -18965,7 +18895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="756" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A756">
         <v>755</v>
       </c>
@@ -18988,7 +18918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="757" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A757">
         <v>756</v>
       </c>
@@ -19011,7 +18941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="758" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A758">
         <v>757</v>
       </c>
@@ -19034,7 +18964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="759" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A759">
         <v>758</v>
       </c>
@@ -19057,7 +18987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="760" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A760">
         <v>759</v>
       </c>
@@ -19080,7 +19010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="761" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A761">
         <v>760</v>
       </c>
@@ -19103,7 +19033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="762" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A762">
         <v>761</v>
       </c>
@@ -19126,7 +19056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="763" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A763">
         <v>762</v>
       </c>
@@ -19149,7 +19079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="764" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A764">
         <v>763</v>
       </c>
@@ -19172,7 +19102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="765" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A765">
         <v>764</v>
       </c>
@@ -19195,7 +19125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="766" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A766">
         <v>765</v>
       </c>
@@ -19218,7 +19148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="767" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A767">
         <v>766</v>
       </c>
@@ -19241,7 +19171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="768" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A768">
         <v>767</v>
       </c>
@@ -19264,7 +19194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="769" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A769">
         <v>768</v>
       </c>
@@ -19287,7 +19217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="770" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A770">
         <v>769</v>
       </c>
@@ -19310,7 +19240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="771" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A771">
         <v>770</v>
       </c>
@@ -19340,7 +19270,7 @@
       </c>
       <c r="J771" s="5"/>
     </row>
-    <row r="772" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A772">
         <v>771</v>
       </c>
@@ -19370,7 +19300,7 @@
       </c>
       <c r="J772" s="5"/>
     </row>
-    <row r="773" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A773">
         <v>772</v>
       </c>
@@ -19393,7 +19323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="774" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A774">
         <v>773</v>
       </c>
@@ -19416,7 +19346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="775" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A775">
         <v>774</v>
       </c>
@@ -19439,7 +19369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="776" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A776">
         <v>775</v>
       </c>
@@ -19458,11 +19388,9 @@
       <c r="I776" s="5">
         <v>1</v>
       </c>
-      <c r="J776" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="777" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J776" s="5"/>
+    </row>
+    <row r="777" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A777">
         <v>776</v>
       </c>
@@ -19485,7 +19413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="778" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A778">
         <v>777</v>
       </c>
@@ -19508,7 +19436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="779" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A779">
         <v>778</v>
       </c>
@@ -19538,7 +19466,7 @@
       </c>
       <c r="J779" s="5"/>
     </row>
-    <row r="780" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A780">
         <v>779</v>
       </c>
@@ -19561,7 +19489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="781" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A781">
         <v>780</v>
       </c>
@@ -19584,7 +19512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="782" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A782">
         <v>781</v>
       </c>
@@ -19607,7 +19535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="783" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A783">
         <v>782</v>
       </c>
@@ -19630,7 +19558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="784" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A784">
         <v>783</v>
       </c>
@@ -19653,7 +19581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="785" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A785">
         <v>784</v>
       </c>
@@ -19676,7 +19604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="786" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A786">
         <v>785</v>
       </c>
@@ -19755,7 +19683,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="789" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A789">
         <v>788</v>
       </c>
@@ -19778,7 +19706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="790" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A790">
         <v>789</v>
       </c>
@@ -19801,7 +19729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="791" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A791">
         <v>790</v>
       </c>
@@ -19824,7 +19752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="792" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A792">
         <v>791</v>
       </c>
@@ -19851,7 +19779,7 @@
       </c>
       <c r="J792" s="5"/>
     </row>
-    <row r="793" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A793">
         <v>792</v>
       </c>
@@ -19874,7 +19802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="794" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A794">
         <v>793</v>
       </c>
@@ -19897,7 +19825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="795" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A795">
         <v>794</v>
       </c>
@@ -19920,7 +19848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="796" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A796">
         <v>795</v>
       </c>
@@ -19943,7 +19871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="797" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A797">
         <v>796</v>
       </c>
@@ -19966,7 +19894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="798" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A798">
         <v>797</v>
       </c>
@@ -19989,7 +19917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="799" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A799">
         <v>798</v>
       </c>
@@ -20012,7 +19940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="800" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A800">
         <v>799</v>
       </c>
@@ -20035,7 +19963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="801" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A801">
         <v>800</v>
       </c>
@@ -20061,7 +19989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="802" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A802">
         <v>801</v>
       </c>
@@ -20087,7 +20015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="803" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A803">
         <v>802</v>
       </c>
@@ -20110,7 +20038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="804" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A804">
         <v>803</v>
       </c>
@@ -20133,7 +20061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="805" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A805">
         <v>804</v>
       </c>
@@ -20152,11 +20080,9 @@
       <c r="I805" s="5">
         <v>1</v>
       </c>
-      <c r="J805" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="806" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J805" s="5"/>
+    </row>
+    <row r="806" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A806">
         <v>805</v>
       </c>
@@ -20179,7 +20105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="807" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A807">
         <v>806</v>
       </c>
@@ -20206,7 +20132,7 @@
       </c>
       <c r="J807" s="5"/>
     </row>
-    <row r="808" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A808">
         <v>807</v>
       </c>
@@ -20229,7 +20155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="809" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A809">
         <v>808</v>
       </c>
@@ -20252,7 +20178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="810" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A810">
         <v>809</v>
       </c>
@@ -20275,7 +20201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="811" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A811">
         <v>810</v>
       </c>
@@ -20298,7 +20224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="812" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A812">
         <v>811</v>
       </c>
@@ -20325,7 +20251,7 @@
       </c>
       <c r="J812" s="5"/>
     </row>
-    <row r="813" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A813">
         <v>812</v>
       </c>
@@ -20348,7 +20274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="814" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A814">
         <v>813</v>
       </c>
@@ -20400,10 +20326,10 @@
       <c r="H815" s="8"/>
       <c r="I815" s="8"/>
       <c r="J815" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="816" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="816" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A816">
         <v>815</v>
       </c>
@@ -20426,7 +20352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="817" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A817">
         <v>816</v>
       </c>
@@ -20449,7 +20375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="818" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A818">
         <v>817</v>
       </c>
@@ -20472,7 +20398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="819" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A819">
         <v>818</v>
       </c>
@@ -20495,7 +20421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="820" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A820">
         <v>819</v>
       </c>
@@ -20518,7 +20444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="821" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A821">
         <v>820</v>
       </c>
@@ -20541,7 +20467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="822" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A822">
         <v>821</v>
       </c>
@@ -20564,7 +20490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="823" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A823">
         <v>822</v>
       </c>
@@ -20587,7 +20513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="824" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A824">
         <v>823</v>
       </c>
@@ -20610,7 +20536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="825" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A825">
         <v>824</v>
       </c>
@@ -20633,7 +20559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="826" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A826">
         <v>825</v>
       </c>
@@ -20660,7 +20586,7 @@
       </c>
       <c r="J826" s="5"/>
     </row>
-    <row r="827" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A827">
         <v>826</v>
       </c>
@@ -20683,7 +20609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="828" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A828">
         <v>827</v>
       </c>
@@ -20713,7 +20639,7 @@
       </c>
       <c r="J828" s="5"/>
     </row>
-    <row r="829" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A829">
         <v>828</v>
       </c>
@@ -20736,7 +20662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="830" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A830">
         <v>829</v>
       </c>
@@ -20759,7 +20685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="831" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A831">
         <v>830</v>
       </c>
@@ -20782,7 +20708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="832" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A832">
         <v>831</v>
       </c>
@@ -20805,7 +20731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="833" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A833">
         <v>832</v>
       </c>
@@ -20824,11 +20750,9 @@
       <c r="I833" s="5">
         <v>1</v>
       </c>
-      <c r="J833" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="834" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J833" s="5"/>
+    </row>
+    <row r="834" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A834">
         <v>833</v>
       </c>
@@ -20851,7 +20775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="835" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A835">
         <v>834</v>
       </c>
@@ -20874,7 +20798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="836" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A836">
         <v>835</v>
       </c>
@@ -20897,7 +20821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="837" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A837">
         <v>836</v>
       </c>
@@ -20923,7 +20847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="838" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A838">
         <v>837</v>
       </c>
@@ -20946,7 +20870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="839" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A839">
         <v>838</v>
       </c>
@@ -20999,12 +20923,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="841" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A841">
         <v>840</v>
       </c>
       <c r="B841" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C841" t="s">
         <v>117</v>
@@ -21022,12 +20946,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="842" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A842">
         <v>841</v>
       </c>
       <c r="B842" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C842" t="s">
         <v>107</v>
@@ -21050,7 +20974,7 @@
         <v>842</v>
       </c>
       <c r="B843" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C843" s="8" t="s">
         <v>108</v>
@@ -21070,15 +20994,15 @@
       <c r="H843" s="8"/>
       <c r="I843" s="8"/>
       <c r="J843" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="844" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="844" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A844">
         <v>843</v>
       </c>
       <c r="B844" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C844" t="s">
         <v>117</v>
@@ -21096,12 +21020,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="845" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A845">
         <v>844</v>
       </c>
       <c r="B845" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C845" t="s">
         <v>117</v>
@@ -21119,12 +21043,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="846" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A846">
         <v>845</v>
       </c>
       <c r="B846" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C846" t="s">
         <v>117</v>
@@ -21142,12 +21066,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="847" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A847">
         <v>846</v>
       </c>
       <c r="B847" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C847" t="s">
         <v>117</v>
@@ -21165,12 +21089,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="848" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A848">
         <v>847</v>
       </c>
       <c r="B848" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C848" t="s">
         <v>117</v>
@@ -21188,12 +21112,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="849" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A849">
         <v>848</v>
       </c>
       <c r="B849" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C849" t="s">
         <v>117</v>
@@ -21211,12 +21135,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="850" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A850">
         <v>849</v>
       </c>
       <c r="B850" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C850" t="s">
         <v>117</v>
@@ -21234,12 +21158,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="851" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A851">
         <v>850</v>
       </c>
       <c r="B851" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C851" t="s">
         <v>117</v>
@@ -21262,7 +21186,7 @@
         <v>851</v>
       </c>
       <c r="B852" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C852" s="2" t="s">
         <v>117</v>
@@ -21285,12 +21209,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="853" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A853">
         <v>852</v>
       </c>
       <c r="B853" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C853" t="s">
         <v>117</v>
@@ -21308,12 +21232,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="854" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A854">
         <v>853</v>
       </c>
       <c r="B854" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C854" t="s">
         <v>117</v>
@@ -21331,12 +21255,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="855" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A855">
         <v>854</v>
       </c>
       <c r="B855" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C855" t="s">
         <v>117</v>
@@ -21354,12 +21278,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="856" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A856">
         <v>855</v>
       </c>
       <c r="B856" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C856" t="s">
         <v>117</v>
@@ -21386,7 +21310,7 @@
         <v>856</v>
       </c>
       <c r="B857" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C857" s="2" t="s">
         <v>117</v>
@@ -21409,12 +21333,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="858" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A858">
         <v>857</v>
       </c>
       <c r="B858" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C858" t="s">
         <v>117</v>
@@ -21432,12 +21356,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="859" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A859">
         <v>858</v>
       </c>
       <c r="B859" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C859" t="s">
         <v>117</v>
@@ -21455,12 +21379,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="860" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A860">
         <v>859</v>
       </c>
       <c r="B860" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C860" t="s">
         <v>117</v>
@@ -21478,7 +21402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="861" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A861">
         <v>860</v>
       </c>
@@ -21497,11 +21421,9 @@
       <c r="I861" s="5">
         <v>1</v>
       </c>
-      <c r="J861" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="862" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J861" s="5"/>
+    </row>
+    <row r="862" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A862">
         <v>861</v>
       </c>
@@ -21524,15 +21446,15 @@
         <v>1</v>
       </c>
       <c r="J862" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="863" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="863" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A863">
         <v>862</v>
       </c>
       <c r="B863" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C863" t="s">
         <v>117</v>
@@ -21553,7 +21475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="864" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A864">
         <v>863</v>
       </c>
@@ -21579,12 +21501,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="865" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A865">
         <v>864</v>
       </c>
       <c r="B865" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C865" t="s">
         <v>117</v>
@@ -21602,12 +21524,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="866" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A866">
         <v>865</v>
       </c>
       <c r="B866" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C866" t="s">
         <v>117</v>
@@ -21628,12 +21550,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="867" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A867">
         <v>866</v>
       </c>
       <c r="B867" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C867" t="s">
         <v>117</v>
@@ -21651,12 +21573,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="868" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A868">
         <v>867</v>
       </c>
       <c r="B868" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C868" t="s">
         <v>117</v>
@@ -21681,12 +21603,12 @@
       </c>
       <c r="J868" s="5"/>
     </row>
-    <row r="869" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A869">
         <v>868</v>
       </c>
       <c r="B869" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C869" t="s">
         <v>107</v>
@@ -21704,12 +21626,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="870" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A870">
         <v>869</v>
       </c>
       <c r="B870" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C870" t="s">
         <v>107</v>
@@ -21727,7 +21649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="871" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A871">
         <v>870</v>
       </c>
@@ -21746,16 +21668,14 @@
       <c r="I871" s="5">
         <v>1</v>
       </c>
-      <c r="J871" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="872" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J871" s="5"/>
+    </row>
+    <row r="872" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A872">
         <v>871</v>
       </c>
       <c r="B872" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C872" t="s">
         <v>107</v>
@@ -21773,12 +21693,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="873" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A873">
         <v>872</v>
       </c>
       <c r="B873" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C873" t="s">
         <v>107</v>
@@ -21796,12 +21716,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="874" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A874">
         <v>873</v>
       </c>
       <c r="B874" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C874" t="s">
         <v>107</v>
@@ -21822,12 +21742,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="875" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A875">
         <v>874</v>
       </c>
       <c r="B875" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C875" t="s">
         <v>107</v>
@@ -21852,12 +21772,12 @@
       </c>
       <c r="J875" s="5"/>
     </row>
-    <row r="876" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A876">
         <v>875</v>
       </c>
       <c r="B876" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C876" t="s">
         <v>107</v>
@@ -21878,12 +21798,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="877" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A877">
         <v>876</v>
       </c>
       <c r="B877" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C877" t="s">
         <v>107</v>
@@ -21901,7 +21821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="878" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A878">
         <v>877</v>
       </c>
@@ -21920,16 +21840,14 @@
       <c r="I878" s="5">
         <v>1</v>
       </c>
-      <c r="J878" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="879" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J878" s="5"/>
+    </row>
+    <row r="879" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A879">
         <v>878</v>
       </c>
       <c r="B879" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C879" t="s">
         <v>108</v>
@@ -21947,12 +21865,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="880" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A880">
         <v>879</v>
       </c>
       <c r="B880" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C880" t="s">
         <v>108</v>
@@ -21970,12 +21888,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="881" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A881">
         <v>880</v>
       </c>
       <c r="B881" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C881" t="s">
         <v>108</v>
@@ -21993,7 +21911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="882" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A882">
         <v>881</v>
       </c>
@@ -22012,16 +21930,14 @@
       <c r="I882" s="5">
         <v>1</v>
       </c>
-      <c r="J882" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="883" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J882" s="5"/>
+    </row>
+    <row r="883" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A883">
         <v>882</v>
       </c>
       <c r="B883" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C883" t="s">
         <v>108</v>
@@ -22039,12 +21955,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="884" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A884">
         <v>883</v>
       </c>
       <c r="B884" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C884" t="s">
         <v>108</v>
@@ -22062,12 +21978,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="885" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A885">
         <v>884</v>
       </c>
       <c r="B885" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C885" t="s">
         <v>108</v>
@@ -22085,12 +22001,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="886" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A886">
         <v>885</v>
       </c>
       <c r="B886" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C886" t="s">
         <v>108</v>
@@ -22112,12 +22028,12 @@
       </c>
       <c r="J886" s="5"/>
     </row>
-    <row r="887" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A887">
         <v>886</v>
       </c>
       <c r="B887" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C887" t="s">
         <v>108</v>
@@ -22135,12 +22051,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="888" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A888">
         <v>887</v>
       </c>
       <c r="B888" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C888" t="s">
         <v>108</v>

--- a/public/data/PUBLICACION CONVOCATORIA.xlsx
+++ b/public/data/PUBLICACION CONVOCATORIA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026\ESFM\INSTITUCIONALIZACIÓN\BASE OFICIAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PROFE-JP\Desktop\PROYECTO\sistema_comparativo\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3206FF0F-4C91-4E58-B859-03FB138B344C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869B14E8-3588-4F8B-A5C4-D8C038AAF6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{928717D9-E10C-4759-930F-0D125842C64E}"/>
   </bookViews>
@@ -401,9 +401,6 @@
     <t>AÑO</t>
   </si>
   <si>
-    <t>INAMOBILIDAD</t>
-  </si>
-  <si>
     <t>REPONER CON COMPULSA</t>
   </si>
   <si>
@@ -432,6 +429,9 @@
   </si>
   <si>
     <t xml:space="preserve">TARIJA    </t>
+  </si>
+  <si>
+    <t>INAMOVILIDAD</t>
   </si>
 </sst>
 </file>
@@ -539,7 +539,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -575,8 +583,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A33032D3-22F0-4889-89B2-2B6957DE8ECA}" name="Tabla5" displayName="Tabla5" ref="A1:K888" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:K888" xr:uid="{A33032D3-22F0-4889-89B2-2B6957DE8ECA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A33032D3-22F0-4889-89B2-2B6957DE8ECA}" name="Tabla5" displayName="Tabla5" ref="A1:K888" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:K888" xr:uid="{A33032D3-22F0-4889-89B2-2B6957DE8ECA}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="TÉCNICO CAJERO"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="10">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J888">
     <sortCondition ref="B1:B888"/>
   </sortState>
@@ -590,7 +607,7 @@
     <tableColumn id="7" xr3:uid="{E2B0CF56-B5EE-4F71-AD74-FE8071EE4967}" name="3 AÑOS"/>
     <tableColumn id="8" xr3:uid="{24B3F4AC-BE58-4BF6-A63A-A46DEB4ECC6E}" name="2 AÑOS"/>
     <tableColumn id="9" xr3:uid="{7A0FC9E7-BB39-43A7-B4F4-8B6FE3D5F100}" name="1 AÑO"/>
-    <tableColumn id="10" xr3:uid="{005BCC62-28BD-4287-9892-604DE4A64D01}" name="SUMA GENERAL" dataDxfId="0">
+    <tableColumn id="10" xr3:uid="{005BCC62-28BD-4287-9892-604DE4A64D01}" name="SUMA GENERAL" dataDxfId="1">
       <calculatedColumnFormula>SUM(Tabla5[[#This Row],[3 AÑOS]:[1 AÑO]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{10744E5C-2216-4BD6-8817-FC23B7AA22EB}" name="DETALLE"/>
@@ -958,13 +975,13 @@
         <v>117</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -991,7 +1008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1018,7 +1035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1045,7 +1062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1072,7 +1089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1099,7 +1116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1126,7 +1143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1153,7 +1170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1180,7 +1197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1207,7 +1224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1234,7 +1251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1261,7 +1278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1288,7 +1305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1315,7 +1332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1342,7 +1359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1369,7 +1386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1394,7 +1411,7 @@
       </c>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1421,7 +1438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1448,7 +1465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1475,7 +1492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1502,7 +1519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1533,7 +1550,7 @@
       </c>
       <c r="K22" s="5"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1567,7 +1584,7 @@
       </c>
       <c r="K23" s="5"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1594,7 +1611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1621,7 +1638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1652,7 +1669,7 @@
       </c>
       <c r="K26" s="5"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1679,7 +1696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1706,7 +1723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1733,7 +1750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1760,7 +1777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1787,7 +1804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1814,7 +1831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1841,7 +1858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1868,7 +1885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1895,7 +1912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1922,7 +1939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1949,7 +1966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1976,7 +1993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2007,7 +2024,7 @@
       </c>
       <c r="K39" s="5"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2038,7 +2055,7 @@
       </c>
       <c r="K40" s="5"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2068,7 +2085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2095,7 +2112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2122,7 +2139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2149,7 +2166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2176,7 +2193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2203,7 +2220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2233,7 +2250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2264,7 +2281,7 @@
       </c>
       <c r="K48" s="5"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2291,7 +2308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2318,7 +2335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2349,7 +2366,7 @@
       </c>
       <c r="K51" s="5"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2376,7 +2393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2403,7 +2420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2430,7 +2447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2457,7 +2474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2484,7 +2501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2511,7 +2528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2538,7 +2555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2572,7 +2589,7 @@
       </c>
       <c r="K59" s="5"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2599,7 +2616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2626,7 +2643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2657,7 +2674,7 @@
       </c>
       <c r="K62" s="5"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2684,7 +2701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2718,7 +2735,7 @@
       </c>
       <c r="K64" s="5"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2745,7 +2762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2772,7 +2789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2799,7 +2816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2828,10 +2845,10 @@
         <v>1</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2858,7 +2875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2885,7 +2902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2912,7 +2929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2939,7 +2956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2966,7 +2983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2993,7 +3010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3018,7 +3035,7 @@
       </c>
       <c r="K75" s="5"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3045,7 +3062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3072,7 +3089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3099,7 +3116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3126,7 +3143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3151,7 +3168,7 @@
       </c>
       <c r="K80" s="5"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3176,7 +3193,7 @@
       </c>
       <c r="K81" s="5"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3203,7 +3220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3230,7 +3247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -3257,7 +3274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3287,7 +3304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3314,7 +3331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3341,7 +3358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3372,7 +3389,7 @@
       </c>
       <c r="K88" s="5"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3399,7 +3416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3428,10 +3445,10 @@
         <v>2</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3458,7 +3475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3485,7 +3502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3512,7 +3529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3539,7 +3556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3566,7 +3583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3593,7 +3610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3620,7 +3637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3647,7 +3664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3674,7 +3691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3701,7 +3718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3728,7 +3745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -3755,7 +3772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -3782,7 +3799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -3809,7 +3826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -3836,7 +3853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -3863,7 +3880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -3888,7 +3905,7 @@
       </c>
       <c r="K107" s="5"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -3915,7 +3932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -3942,7 +3959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -3969,7 +3986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -3994,7 +4011,7 @@
       </c>
       <c r="K111" s="5"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -4021,7 +4038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -4048,7 +4065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -4075,7 +4092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -4109,7 +4126,7 @@
       </c>
       <c r="K115" s="5"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -4136,7 +4153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -4163,7 +4180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -4188,7 +4205,7 @@
       </c>
       <c r="K118" s="5"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -4215,7 +4232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -4242,7 +4259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -4269,7 +4286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -4296,7 +4313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -4323,7 +4340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -4350,7 +4367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -4377,7 +4394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -4404,7 +4421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -4431,7 +4448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -4458,7 +4475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -4485,7 +4502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -4512,7 +4529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -4542,7 +4559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -4569,7 +4586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -4596,7 +4613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -4623,7 +4640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -4650,7 +4667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -4675,7 +4692,7 @@
       </c>
       <c r="K136" s="5"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -4700,7 +4717,7 @@
       </c>
       <c r="K137" s="5"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -4731,7 +4748,7 @@
       </c>
       <c r="K138" s="5"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -4761,7 +4778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -4788,7 +4805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="8">
         <v>140</v>
       </c>
@@ -4817,10 +4834,10 @@
         <v>1</v>
       </c>
       <c r="K141" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -4847,7 +4864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -4874,7 +4891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -4901,7 +4918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -4928,7 +4945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -4955,7 +4972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -4982,7 +4999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -5009,7 +5026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -5065,10 +5082,10 @@
         <v>1</v>
       </c>
       <c r="K150" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -5095,7 +5112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -5122,7 +5139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -5149,7 +5166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -5176,7 +5193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -5203,7 +5220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -5230,7 +5247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -5257,7 +5274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -5284,7 +5301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -5311,7 +5328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -5338,7 +5355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -5369,7 +5386,7 @@
       </c>
       <c r="K161" s="5"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -5396,7 +5413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -5426,7 +5443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -5453,7 +5470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -5480,7 +5497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -5507,7 +5524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -5538,7 +5555,7 @@
       </c>
       <c r="K167" s="5"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -5569,7 +5586,7 @@
       </c>
       <c r="K168" s="5"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -5596,7 +5613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -5623,7 +5640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -5650,7 +5667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -5677,7 +5694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -5704,7 +5721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -5731,7 +5748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -5758,7 +5775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -5785,7 +5802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -5812,7 +5829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -5839,7 +5856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -5866,7 +5883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -5893,7 +5910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -5920,7 +5937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -5947,7 +5964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -5978,7 +5995,7 @@
       </c>
       <c r="K183" s="5"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -6005,7 +6022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -6032,7 +6049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -6059,7 +6076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -6086,7 +6103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -6116,7 +6133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -6150,7 +6167,7 @@
       </c>
       <c r="K189" s="5"/>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -6177,7 +6194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -6206,10 +6223,10 @@
         <v>1</v>
       </c>
       <c r="K191" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -6234,7 +6251,7 @@
       </c>
       <c r="K192" s="5"/>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -6261,7 +6278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -6288,7 +6305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -6315,7 +6332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -6342,7 +6359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -6369,7 +6386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -6396,7 +6413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -6423,7 +6440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -6450,7 +6467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -6477,7 +6494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -6504,7 +6521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -6531,7 +6548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -6558,7 +6575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -6585,7 +6602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -6612,7 +6629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -6639,7 +6656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -6670,7 +6687,7 @@
       </c>
       <c r="K208" s="5"/>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -6697,7 +6714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -6724,7 +6741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -6751,7 +6768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -6782,7 +6799,7 @@
       </c>
       <c r="K212" s="5"/>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -6809,7 +6826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -6836,7 +6853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -6870,7 +6887,7 @@
       </c>
       <c r="K215" s="5"/>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -6897,7 +6914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -6924,7 +6941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -6951,7 +6968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -6978,7 +6995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -7003,7 +7020,7 @@
       </c>
       <c r="K220" s="5"/>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -7037,7 +7054,7 @@
       </c>
       <c r="K221" s="5"/>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -7064,7 +7081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -7085,7 +7102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -7112,7 +7129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -7141,10 +7158,10 @@
         <v>1</v>
       </c>
       <c r="K225" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -7174,7 +7191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -7201,7 +7218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -7228,7 +7245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -7255,7 +7272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -7282,7 +7299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -7313,7 +7330,7 @@
       </c>
       <c r="K231" s="5"/>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -7340,7 +7357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -7367,7 +7384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -7394,10 +7411,10 @@
         <v>0</v>
       </c>
       <c r="K234" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -7427,7 +7444,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -7454,7 +7471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -7481,7 +7498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -7508,7 +7525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -7535,7 +7552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -7562,7 +7579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -7592,7 +7609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -7623,7 +7640,7 @@
       </c>
       <c r="K242" s="5"/>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -7652,10 +7669,10 @@
         <v>2</v>
       </c>
       <c r="K243" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -7682,7 +7699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -7709,7 +7726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
@@ -7736,7 +7753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
@@ -7763,7 +7780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
@@ -7790,7 +7807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
@@ -7817,7 +7834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
@@ -7844,7 +7861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
@@ -7878,7 +7895,7 @@
       </c>
       <c r="K251" s="5"/>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
@@ -7912,7 +7929,7 @@
       </c>
       <c r="K252" s="5"/>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -7939,7 +7956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -7953,7 +7970,7 @@
         <v>7</v>
       </c>
       <c r="E254" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F254">
         <v>2026</v>
@@ -7966,7 +7983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -7993,7 +8010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -8020,7 +8037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -8047,7 +8064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -8074,7 +8091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -8101,7 +8118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -8128,7 +8145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -8155,7 +8172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -8182,7 +8199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
@@ -8209,7 +8226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
@@ -8238,10 +8255,10 @@
         <v>1</v>
       </c>
       <c r="K264" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -8268,7 +8285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
@@ -8297,10 +8314,10 @@
         <v>1</v>
       </c>
       <c r="K266" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -8327,7 +8344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
@@ -8354,7 +8371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -8381,7 +8398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -8408,7 +8425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -8438,7 +8455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -8463,7 +8480,7 @@
       </c>
       <c r="K272" s="5"/>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
@@ -8490,7 +8507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -8517,7 +8534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
@@ -8551,7 +8568,7 @@
       </c>
       <c r="K275" s="5"/>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
@@ -8578,7 +8595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
@@ -8609,7 +8626,7 @@
       </c>
       <c r="K277" s="5"/>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>277</v>
       </c>
@@ -8636,7 +8653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
@@ -8663,7 +8680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
@@ -8690,7 +8707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
@@ -8717,7 +8734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
@@ -8744,7 +8761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>282</v>
       </c>
@@ -8771,7 +8788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>283</v>
       </c>
@@ -8798,7 +8815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>284</v>
       </c>
@@ -8825,7 +8842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>285</v>
       </c>
@@ -8852,7 +8869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>286</v>
       </c>
@@ -8879,7 +8896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>287</v>
       </c>
@@ -8906,7 +8923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>288</v>
       </c>
@@ -8933,7 +8950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>289</v>
       </c>
@@ -8960,7 +8977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>290</v>
       </c>
@@ -8991,7 +9008,7 @@
       </c>
       <c r="K291" s="5"/>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>291</v>
       </c>
@@ -9016,7 +9033,7 @@
       </c>
       <c r="K292" s="5"/>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>292</v>
       </c>
@@ -9043,7 +9060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>293</v>
       </c>
@@ -9070,7 +9087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>294</v>
       </c>
@@ -9097,7 +9114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>295</v>
       </c>
@@ -9124,7 +9141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>296</v>
       </c>
@@ -9151,7 +9168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>297</v>
       </c>
@@ -9182,10 +9199,10 @@
         <v>2</v>
       </c>
       <c r="K298" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>298</v>
       </c>
@@ -9219,7 +9236,7 @@
       </c>
       <c r="K299" s="5"/>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>299</v>
       </c>
@@ -9246,7 +9263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>300</v>
       </c>
@@ -9273,7 +9290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>301</v>
       </c>
@@ -9300,7 +9317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>302</v>
       </c>
@@ -9327,7 +9344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>303</v>
       </c>
@@ -9354,7 +9371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>304</v>
       </c>
@@ -9381,7 +9398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>305</v>
       </c>
@@ -9408,7 +9425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>306</v>
       </c>
@@ -9435,7 +9452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>307</v>
       </c>
@@ -9462,7 +9479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>308</v>
       </c>
@@ -9489,7 +9506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>309</v>
       </c>
@@ -9516,7 +9533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>310</v>
       </c>
@@ -9543,7 +9560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>311</v>
       </c>
@@ -9570,7 +9587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>312</v>
       </c>
@@ -9597,7 +9614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>313</v>
       </c>
@@ -9624,7 +9641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>314</v>
       </c>
@@ -9651,7 +9668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>315</v>
       </c>
@@ -9678,7 +9695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>316</v>
       </c>
@@ -9705,7 +9722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>317</v>
       </c>
@@ -9732,7 +9749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>318</v>
       </c>
@@ -9759,7 +9776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>319</v>
       </c>
@@ -9789,7 +9806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>320</v>
       </c>
@@ -9820,7 +9837,7 @@
       </c>
       <c r="K321" s="5"/>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>321</v>
       </c>
@@ -9850,7 +9867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>322</v>
       </c>
@@ -9877,7 +9894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>323</v>
       </c>
@@ -9904,7 +9921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>324</v>
       </c>
@@ -9931,7 +9948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>325</v>
       </c>
@@ -9958,7 +9975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>326</v>
       </c>
@@ -9989,7 +10006,7 @@
       </c>
       <c r="K327" s="5"/>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>327</v>
       </c>
@@ -10016,7 +10033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>328</v>
       </c>
@@ -10050,7 +10067,7 @@
       </c>
       <c r="K329" s="5"/>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>329</v>
       </c>
@@ -10077,7 +10094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>330</v>
       </c>
@@ -10104,7 +10121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>331</v>
       </c>
@@ -10131,7 +10148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>332</v>
       </c>
@@ -10158,7 +10175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="8">
         <v>333</v>
       </c>
@@ -10187,10 +10204,10 @@
         <v>1</v>
       </c>
       <c r="K334" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>334</v>
       </c>
@@ -10217,7 +10234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>335</v>
       </c>
@@ -10244,7 +10261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>336</v>
       </c>
@@ -10271,7 +10288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>337</v>
       </c>
@@ -10298,7 +10315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>338</v>
       </c>
@@ -10325,7 +10342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>339</v>
       </c>
@@ -10354,10 +10371,10 @@
         <v>1</v>
       </c>
       <c r="K340" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>340</v>
       </c>
@@ -10384,7 +10401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>341</v>
       </c>
@@ -10415,10 +10432,10 @@
         <v>2</v>
       </c>
       <c r="K342" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>342</v>
       </c>
@@ -10449,7 +10466,7 @@
       </c>
       <c r="K343" s="5"/>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>343</v>
       </c>
@@ -10476,7 +10493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>344</v>
       </c>
@@ -10503,7 +10520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>345</v>
       </c>
@@ -10530,7 +10547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>346</v>
       </c>
@@ -10559,10 +10576,10 @@
         <v>1</v>
       </c>
       <c r="K347" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="348" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>347</v>
       </c>
@@ -10593,10 +10610,10 @@
         <v>3</v>
       </c>
       <c r="K348" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="349" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>348</v>
       </c>
@@ -10630,7 +10647,7 @@
       </c>
       <c r="K349" s="5"/>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>349</v>
       </c>
@@ -10657,7 +10674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>350</v>
       </c>
@@ -10684,7 +10701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>351</v>
       </c>
@@ -10711,7 +10728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>352</v>
       </c>
@@ -10738,7 +10755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>353</v>
       </c>
@@ -10765,7 +10782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>354</v>
       </c>
@@ -10792,7 +10809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>355</v>
       </c>
@@ -10819,7 +10836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>356</v>
       </c>
@@ -10846,7 +10863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>357</v>
       </c>
@@ -10873,7 +10890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>358</v>
       </c>
@@ -10900,7 +10917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>359</v>
       </c>
@@ -10927,7 +10944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>360</v>
       </c>
@@ -10954,7 +10971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>361</v>
       </c>
@@ -10981,7 +10998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>362</v>
       </c>
@@ -11008,7 +11025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>363</v>
       </c>
@@ -11035,7 +11052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>364</v>
       </c>
@@ -11060,7 +11077,7 @@
       </c>
       <c r="K365" s="5"/>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>365</v>
       </c>
@@ -11087,7 +11104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>366</v>
       </c>
@@ -11114,7 +11131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>367</v>
       </c>
@@ -11145,7 +11162,7 @@
       </c>
       <c r="K368" s="5"/>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>368</v>
       </c>
@@ -11172,7 +11189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>369</v>
       </c>
@@ -11199,7 +11216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>370</v>
       </c>
@@ -11226,7 +11243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>371</v>
       </c>
@@ -11247,7 +11264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>372</v>
       </c>
@@ -11274,7 +11291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>373</v>
       </c>
@@ -11295,7 +11312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>374</v>
       </c>
@@ -11326,10 +11343,10 @@
         <v>3</v>
       </c>
       <c r="K375" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>375</v>
       </c>
@@ -11363,7 +11380,7 @@
       </c>
       <c r="K376" s="5"/>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>376</v>
       </c>
@@ -11390,7 +11407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>377</v>
       </c>
@@ -11417,7 +11434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>378</v>
       </c>
@@ -11444,7 +11461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>379</v>
       </c>
@@ -11478,7 +11495,7 @@
       </c>
       <c r="K380" s="5"/>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>380</v>
       </c>
@@ -11505,7 +11522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>381</v>
       </c>
@@ -11532,7 +11549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>382</v>
       </c>
@@ -11559,7 +11576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>383</v>
       </c>
@@ -11586,7 +11603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>384</v>
       </c>
@@ -11613,7 +11630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>385</v>
       </c>
@@ -11640,7 +11657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>386</v>
       </c>
@@ -11667,7 +11684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>387</v>
       </c>
@@ -11694,7 +11711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>388</v>
       </c>
@@ -11721,7 +11738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>389</v>
       </c>
@@ -11748,7 +11765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>390</v>
       </c>
@@ -11775,7 +11792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>391</v>
       </c>
@@ -11802,7 +11819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>392</v>
       </c>
@@ -11827,7 +11844,7 @@
       </c>
       <c r="K393" s="5"/>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>393</v>
       </c>
@@ -11854,7 +11871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>394</v>
       </c>
@@ -11881,7 +11898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>395</v>
       </c>
@@ -11908,7 +11925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>396</v>
       </c>
@@ -11935,7 +11952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>397</v>
       </c>
@@ -11962,7 +11979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>398</v>
       </c>
@@ -11989,7 +12006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>399</v>
       </c>
@@ -12019,7 +12036,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>400</v>
       </c>
@@ -12053,7 +12070,7 @@
       </c>
       <c r="K401" s="5"/>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>401</v>
       </c>
@@ -12080,7 +12097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>402</v>
       </c>
@@ -12111,7 +12128,7 @@
       </c>
       <c r="K403" s="5"/>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>403</v>
       </c>
@@ -12142,10 +12159,10 @@
         <v>2</v>
       </c>
       <c r="K404" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="405" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>404</v>
       </c>
@@ -12172,7 +12189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>405</v>
       </c>
@@ -12199,7 +12216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>406</v>
       </c>
@@ -12226,7 +12243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>407</v>
       </c>
@@ -12253,7 +12270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>408</v>
       </c>
@@ -12280,7 +12297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>409</v>
       </c>
@@ -12307,7 +12324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>410</v>
       </c>
@@ -12334,7 +12351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>411</v>
       </c>
@@ -12361,7 +12378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>412</v>
       </c>
@@ -12388,7 +12405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>413</v>
       </c>
@@ -12415,7 +12432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>414</v>
       </c>
@@ -12442,7 +12459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>415</v>
       </c>
@@ -12469,7 +12486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>416</v>
       </c>
@@ -12496,7 +12513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>417</v>
       </c>
@@ -12523,7 +12540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>418</v>
       </c>
@@ -12550,7 +12567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>419</v>
       </c>
@@ -12577,7 +12594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>420</v>
       </c>
@@ -12604,7 +12621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>421</v>
       </c>
@@ -12631,7 +12648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>422</v>
       </c>
@@ -12665,7 +12682,7 @@
       </c>
       <c r="K423" s="5"/>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>423</v>
       </c>
@@ -12692,7 +12709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>424</v>
       </c>
@@ -12719,7 +12736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>425</v>
       </c>
@@ -12746,7 +12763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>426</v>
       </c>
@@ -12775,10 +12792,10 @@
         <v>1</v>
       </c>
       <c r="K427" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="428" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>427</v>
       </c>
@@ -12805,7 +12822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>428</v>
       </c>
@@ -12836,7 +12853,7 @@
       </c>
       <c r="K429" s="5"/>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>429</v>
       </c>
@@ -12863,7 +12880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>430</v>
       </c>
@@ -12890,7 +12907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>431</v>
       </c>
@@ -12917,7 +12934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>432</v>
       </c>
@@ -12944,7 +12961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>433</v>
       </c>
@@ -12971,7 +12988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>434</v>
       </c>
@@ -12998,7 +13015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>435</v>
       </c>
@@ -13025,7 +13042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>436</v>
       </c>
@@ -13052,7 +13069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>437</v>
       </c>
@@ -13079,7 +13096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>438</v>
       </c>
@@ -13106,7 +13123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>439</v>
       </c>
@@ -13133,7 +13150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>440</v>
       </c>
@@ -13167,7 +13184,7 @@
       </c>
       <c r="K441" s="5"/>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>441</v>
       </c>
@@ -13198,7 +13215,7 @@
       </c>
       <c r="K442" s="5"/>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>442</v>
       </c>
@@ -13225,7 +13242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>443</v>
       </c>
@@ -13252,7 +13269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>444</v>
       </c>
@@ -13279,7 +13296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>445</v>
       </c>
@@ -13306,7 +13323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>446</v>
       </c>
@@ -13333,7 +13350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>447</v>
       </c>
@@ -13360,7 +13377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>448</v>
       </c>
@@ -13391,7 +13408,7 @@
       </c>
       <c r="K449" s="5"/>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>449</v>
       </c>
@@ -13418,7 +13435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>450</v>
       </c>
@@ -13445,7 +13462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>451</v>
       </c>
@@ -13472,7 +13489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>452</v>
       </c>
@@ -13499,7 +13516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>453</v>
       </c>
@@ -13526,7 +13543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>454</v>
       </c>
@@ -13553,7 +13570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>455</v>
       </c>
@@ -13580,7 +13597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>456</v>
       </c>
@@ -13607,7 +13624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>457</v>
       </c>
@@ -13634,7 +13651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>458</v>
       </c>
@@ -13661,7 +13678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>459</v>
       </c>
@@ -13688,7 +13705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>460</v>
       </c>
@@ -13715,7 +13732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>461</v>
       </c>
@@ -13742,7 +13759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>462</v>
       </c>
@@ -13769,7 +13786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>463</v>
       </c>
@@ -13796,7 +13813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>464</v>
       </c>
@@ -13823,7 +13840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>465</v>
       </c>
@@ -13850,7 +13867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>466</v>
       </c>
@@ -13877,7 +13894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>467</v>
       </c>
@@ -13904,7 +13921,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>468</v>
       </c>
@@ -13931,7 +13948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>469</v>
       </c>
@@ -13958,7 +13975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>470</v>
       </c>
@@ -13985,7 +14002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>471</v>
       </c>
@@ -14012,7 +14029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>472</v>
       </c>
@@ -14039,7 +14056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>473</v>
       </c>
@@ -14073,7 +14090,7 @@
       </c>
       <c r="K474" s="5"/>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>474</v>
       </c>
@@ -14104,7 +14121,7 @@
       </c>
       <c r="K475" s="5"/>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>475</v>
       </c>
@@ -14131,7 +14148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>476</v>
       </c>
@@ -14158,7 +14175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>477</v>
       </c>
@@ -14185,7 +14202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>478</v>
       </c>
@@ -14210,7 +14227,7 @@
       </c>
       <c r="K479" s="5"/>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>479</v>
       </c>
@@ -14237,7 +14254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>480</v>
       </c>
@@ -14264,7 +14281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>481</v>
       </c>
@@ -14291,7 +14308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>482</v>
       </c>
@@ -14318,7 +14335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>483</v>
       </c>
@@ -14345,7 +14362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>484</v>
       </c>
@@ -14372,7 +14389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>485</v>
       </c>
@@ -14399,7 +14416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>486</v>
       </c>
@@ -14426,7 +14443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>487</v>
       </c>
@@ -14453,7 +14470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>488</v>
       </c>
@@ -14480,7 +14497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>489</v>
       </c>
@@ -14507,7 +14524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>490</v>
       </c>
@@ -14534,7 +14551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>491</v>
       </c>
@@ -14561,7 +14578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>492</v>
       </c>
@@ -14586,7 +14603,7 @@
       </c>
       <c r="K493" s="5"/>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>493</v>
       </c>
@@ -14613,7 +14630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>494</v>
       </c>
@@ -14640,7 +14657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>495</v>
       </c>
@@ -14667,7 +14684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>496</v>
       </c>
@@ -14694,7 +14711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>497</v>
       </c>
@@ -14724,7 +14741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>498</v>
       </c>
@@ -14758,7 +14775,7 @@
       </c>
       <c r="K499" s="5"/>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>499</v>
       </c>
@@ -14787,10 +14804,10 @@
         <v>2</v>
       </c>
       <c r="K500" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>500</v>
       </c>
@@ -14815,7 +14832,7 @@
       </c>
       <c r="K501" s="5"/>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>501</v>
       </c>
@@ -14842,7 +14859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>502</v>
       </c>
@@ -14869,7 +14886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>503</v>
       </c>
@@ -14900,10 +14917,10 @@
         <v>2</v>
       </c>
       <c r="K504" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="505" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>504</v>
       </c>
@@ -14933,7 +14950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>505</v>
       </c>
@@ -14960,7 +14977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>506</v>
       </c>
@@ -14987,7 +15004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>507</v>
       </c>
@@ -15014,7 +15031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>508</v>
       </c>
@@ -15041,7 +15058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>509</v>
       </c>
@@ -15075,7 +15092,7 @@
       </c>
       <c r="K510" s="5"/>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>510</v>
       </c>
@@ -15102,7 +15119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>511</v>
       </c>
@@ -15133,7 +15150,7 @@
       </c>
       <c r="K512" s="5"/>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>512</v>
       </c>
@@ -15160,7 +15177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>513</v>
       </c>
@@ -15187,7 +15204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>514</v>
       </c>
@@ -15214,7 +15231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>515</v>
       </c>
@@ -15241,7 +15258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>516</v>
       </c>
@@ -15268,7 +15285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>517</v>
       </c>
@@ -15299,7 +15316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="519" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>518</v>
       </c>
@@ -15326,7 +15343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>519</v>
       </c>
@@ -15353,7 +15370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>520</v>
       </c>
@@ -15380,7 +15397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>521</v>
       </c>
@@ -15407,7 +15424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>522</v>
       </c>
@@ -15434,7 +15451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>523</v>
       </c>
@@ -15465,7 +15482,7 @@
       </c>
       <c r="K524" s="5"/>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>524</v>
       </c>
@@ -15495,7 +15512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>525</v>
       </c>
@@ -15522,7 +15539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>526</v>
       </c>
@@ -15549,7 +15566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>527</v>
       </c>
@@ -15576,7 +15593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>528</v>
       </c>
@@ -15603,7 +15620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>529</v>
       </c>
@@ -15632,10 +15649,10 @@
         <v>1</v>
       </c>
       <c r="K530" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="531" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>530</v>
       </c>
@@ -15662,7 +15679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>531</v>
       </c>
@@ -15718,10 +15735,10 @@
         <v>1</v>
       </c>
       <c r="K533" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="534" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>533</v>
       </c>
@@ -15750,10 +15767,10 @@
         <v>1</v>
       </c>
       <c r="K534" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="535" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>534</v>
       </c>
@@ -15780,7 +15797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>535</v>
       </c>
@@ -15809,10 +15826,10 @@
         <v>1</v>
       </c>
       <c r="K536" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="537" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>536</v>
       </c>
@@ -15839,7 +15856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>537</v>
       </c>
@@ -15868,10 +15885,10 @@
         <v>1</v>
       </c>
       <c r="K538" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="539" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>538</v>
       </c>
@@ -15898,7 +15915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>539</v>
       </c>
@@ -15925,7 +15942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>540</v>
       </c>
@@ -15950,7 +15967,7 @@
       </c>
       <c r="K541" s="5"/>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>541</v>
       </c>
@@ -15984,7 +16001,7 @@
       </c>
       <c r="K542" s="5"/>
     </row>
-    <row r="543" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>542</v>
       </c>
@@ -16011,7 +16028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>543</v>
       </c>
@@ -16038,7 +16055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>544</v>
       </c>
@@ -16065,7 +16082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>545</v>
       </c>
@@ -16098,10 +16115,10 @@
         <v>3</v>
       </c>
       <c r="K546" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="547" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="547" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>546</v>
       </c>
@@ -16128,7 +16145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>547</v>
       </c>
@@ -16162,7 +16179,7 @@
       </c>
       <c r="K548" s="5"/>
     </row>
-    <row r="549" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>548</v>
       </c>
@@ -16189,7 +16206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>549</v>
       </c>
@@ -16216,7 +16233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="551" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>550</v>
       </c>
@@ -16241,7 +16258,7 @@
       </c>
       <c r="K551" s="5"/>
     </row>
-    <row r="552" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>551</v>
       </c>
@@ -16268,7 +16285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>552</v>
       </c>
@@ -16295,7 +16312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>553</v>
       </c>
@@ -16320,7 +16337,7 @@
       </c>
       <c r="K554" s="5"/>
     </row>
-    <row r="555" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>554</v>
       </c>
@@ -16347,7 +16364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="556" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>555</v>
       </c>
@@ -16374,7 +16391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="557" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>556</v>
       </c>
@@ -16401,7 +16418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>557</v>
       </c>
@@ -16432,10 +16449,10 @@
         <v>2</v>
       </c>
       <c r="K558" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="559" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>558</v>
       </c>
@@ -16462,7 +16479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>559</v>
       </c>
@@ -16496,7 +16513,7 @@
       </c>
       <c r="K560" s="5"/>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>560</v>
       </c>
@@ -16523,7 +16540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>561</v>
       </c>
@@ -16554,7 +16571,7 @@
       </c>
       <c r="K562" s="5"/>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>562</v>
       </c>
@@ -16581,7 +16598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>563</v>
       </c>
@@ -16610,10 +16627,10 @@
         <v>1</v>
       </c>
       <c r="K564" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="565" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>564</v>
       </c>
@@ -16638,7 +16655,7 @@
       </c>
       <c r="K565" s="5"/>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>565</v>
       </c>
@@ -16669,7 +16686,7 @@
       </c>
       <c r="K566" s="5"/>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>566</v>
       </c>
@@ -16696,7 +16713,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>567</v>
       </c>
@@ -16723,7 +16740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="569" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>568</v>
       </c>
@@ -16748,7 +16765,7 @@
       </c>
       <c r="K569" s="5"/>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>569</v>
       </c>
@@ -16775,7 +16792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>570</v>
       </c>
@@ -16802,7 +16819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>571</v>
       </c>
@@ -16829,7 +16846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>572</v>
       </c>
@@ -16856,7 +16873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>573</v>
       </c>
@@ -16883,7 +16900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>574</v>
       </c>
@@ -16910,7 +16927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>575</v>
       </c>
@@ -16941,7 +16958,7 @@
       </c>
       <c r="K576" s="5"/>
     </row>
-    <row r="577" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>576</v>
       </c>
@@ -16968,7 +16985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="578" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>577</v>
       </c>
@@ -16999,7 +17016,7 @@
       </c>
       <c r="K578" s="5"/>
     </row>
-    <row r="579" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>578</v>
       </c>
@@ -17026,7 +17043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="580" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>579</v>
       </c>
@@ -17053,7 +17070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="581" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>580</v>
       </c>
@@ -17080,7 +17097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="582" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>581</v>
       </c>
@@ -17109,10 +17126,10 @@
         <v>1</v>
       </c>
       <c r="K582" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="583" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="583" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>582</v>
       </c>
@@ -17139,7 +17156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="584" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>583</v>
       </c>
@@ -17166,7 +17183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="585" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>584</v>
       </c>
@@ -17193,7 +17210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="586" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>585</v>
       </c>
@@ -17220,7 +17237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="587" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>586</v>
       </c>
@@ -17247,7 +17264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>587</v>
       </c>
@@ -17274,7 +17291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="589" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>588</v>
       </c>
@@ -17301,7 +17318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="590" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>589</v>
       </c>
@@ -17328,7 +17345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="591" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>590</v>
       </c>
@@ -17353,7 +17370,7 @@
       </c>
       <c r="K591" s="5"/>
     </row>
-    <row r="592" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>591</v>
       </c>
@@ -17380,7 +17397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="593" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>592</v>
       </c>
@@ -17407,7 +17424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="594" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>593</v>
       </c>
@@ -17434,7 +17451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="595" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>594</v>
       </c>
@@ -17465,10 +17482,10 @@
         <v>2</v>
       </c>
       <c r="K595" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="596" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="596" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>595</v>
       </c>
@@ -17499,7 +17516,7 @@
       </c>
       <c r="K596" s="5"/>
     </row>
-    <row r="597" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>596</v>
       </c>
@@ -17529,7 +17546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="598" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>597</v>
       </c>
@@ -17556,7 +17573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="599" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>598</v>
       </c>
@@ -17586,7 +17603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="600" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>599</v>
       </c>
@@ -17613,7 +17630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="601" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>600</v>
       </c>
@@ -17640,7 +17657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="602" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>601</v>
       </c>
@@ -17667,7 +17684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="603" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>602</v>
       </c>
@@ -17701,7 +17718,7 @@
       </c>
       <c r="K603" s="5"/>
     </row>
-    <row r="604" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>603</v>
       </c>
@@ -17728,7 +17745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="605" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>604</v>
       </c>
@@ -17755,7 +17772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="606" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>605</v>
       </c>
@@ -17782,7 +17799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="607" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>606</v>
       </c>
@@ -17809,7 +17826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="608" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608">
         <v>607</v>
       </c>
@@ -17836,7 +17853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="609" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>608</v>
       </c>
@@ -17863,7 +17880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="610" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>609</v>
       </c>
@@ -17890,7 +17907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="611" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>610</v>
       </c>
@@ -17917,7 +17934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="612" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612">
         <v>611</v>
       </c>
@@ -17944,7 +17961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="613" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>612</v>
       </c>
@@ -17971,7 +17988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="614" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614">
         <v>613</v>
       </c>
@@ -17998,7 +18015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="615" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>614</v>
       </c>
@@ -18025,7 +18042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="616" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616">
         <v>615</v>
       </c>
@@ -18052,7 +18069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>616</v>
       </c>
@@ -18079,7 +18096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="618" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618">
         <v>617</v>
       </c>
@@ -18106,7 +18123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="619" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>618</v>
       </c>
@@ -18136,7 +18153,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="620" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620">
         <v>619</v>
       </c>
@@ -18161,7 +18178,7 @@
       </c>
       <c r="K620" s="5"/>
     </row>
-    <row r="621" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>620</v>
       </c>
@@ -18192,7 +18209,7 @@
       </c>
       <c r="K621" s="5"/>
     </row>
-    <row r="622" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622">
         <v>621</v>
       </c>
@@ -18219,7 +18236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="623" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>622</v>
       </c>
@@ -18246,7 +18263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="624" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624">
         <v>623</v>
       </c>
@@ -18273,7 +18290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="625" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>624</v>
       </c>
@@ -18300,7 +18317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="626" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>625</v>
       </c>
@@ -18327,7 +18344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="627" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>626</v>
       </c>
@@ -18356,10 +18373,10 @@
         <v>1</v>
       </c>
       <c r="K627" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="628" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="628" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628">
         <v>627</v>
       </c>
@@ -18386,7 +18403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="629" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>628</v>
       </c>
@@ -18413,7 +18430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="630" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>629</v>
       </c>
@@ -18440,7 +18457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="631" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>630</v>
       </c>
@@ -18467,7 +18484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="632" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632">
         <v>631</v>
       </c>
@@ -18494,7 +18511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="633" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633">
         <v>632</v>
       </c>
@@ -18523,10 +18540,10 @@
         <v>1</v>
       </c>
       <c r="K633" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="634" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="634" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634">
         <v>633</v>
       </c>
@@ -18553,7 +18570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="635" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635">
         <v>634</v>
       </c>
@@ -18580,7 +18597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="636" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636">
         <v>635</v>
       </c>
@@ -18607,10 +18624,10 @@
         <v>1</v>
       </c>
       <c r="K636" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="637" spans="1:11" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="637" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637">
         <v>636</v>
       </c>
@@ -18637,7 +18654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="638" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638">
         <v>637</v>
       </c>
@@ -18664,7 +18681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="639" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>638</v>
       </c>
@@ -18691,7 +18708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="640" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640">
         <v>639</v>
       </c>
@@ -18718,7 +18735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="641" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641">
         <v>640</v>
       </c>
@@ -18745,7 +18762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="642" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642">
         <v>641</v>
       </c>
@@ -18772,7 +18789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="643" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643">
         <v>642</v>
       </c>
@@ -18799,7 +18816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="644" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644">
         <v>643</v>
       </c>
@@ -18826,7 +18843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="645" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645">
         <v>644</v>
       </c>
@@ -18853,7 +18870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="646" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646">
         <v>645</v>
       </c>
@@ -18887,7 +18904,7 @@
       </c>
       <c r="K646" s="5"/>
     </row>
-    <row r="647" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647">
         <v>646</v>
       </c>
@@ -18912,7 +18929,7 @@
       </c>
       <c r="K647" s="5"/>
     </row>
-    <row r="648" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648">
         <v>647</v>
       </c>
@@ -18939,7 +18956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="649" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649">
         <v>648</v>
       </c>
@@ -18966,7 +18983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="650" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650">
         <v>649</v>
       </c>
@@ -18993,7 +19010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="651" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651">
         <v>650</v>
       </c>
@@ -19027,7 +19044,7 @@
       </c>
       <c r="K651" s="5"/>
     </row>
-    <row r="652" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652">
         <v>651</v>
       </c>
@@ -19058,7 +19075,7 @@
       </c>
       <c r="K652" s="5"/>
     </row>
-    <row r="653" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653">
         <v>652</v>
       </c>
@@ -19085,7 +19102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="654" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654">
         <v>653</v>
       </c>
@@ -19112,7 +19129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="655" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655">
         <v>654</v>
       </c>
@@ -19139,7 +19156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="656" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656">
         <v>655</v>
       </c>
@@ -19166,7 +19183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="657" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657">
         <v>656</v>
       </c>
@@ -19222,10 +19239,10 @@
         <v>1</v>
       </c>
       <c r="K658" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="659" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="659" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659">
         <v>658</v>
       </c>
@@ -19252,7 +19269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="660" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660">
         <v>659</v>
       </c>
@@ -19279,7 +19296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="661" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661">
         <v>660</v>
       </c>
@@ -19306,7 +19323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="662" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662">
         <v>661</v>
       </c>
@@ -19333,7 +19350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="663" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663">
         <v>662</v>
       </c>
@@ -19360,7 +19377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="664" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664">
         <v>663</v>
       </c>
@@ -19389,10 +19406,10 @@
         <v>1</v>
       </c>
       <c r="K664" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="665" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="665" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665">
         <v>664</v>
       </c>
@@ -19419,7 +19436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="666" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666">
         <v>665</v>
       </c>
@@ -19446,7 +19463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="667" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667">
         <v>666</v>
       </c>
@@ -19473,7 +19490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="668" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668">
         <v>667</v>
       </c>
@@ -19500,7 +19517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="669" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669">
         <v>668</v>
       </c>
@@ -19527,7 +19544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="670" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670">
         <v>669</v>
       </c>
@@ -19554,7 +19571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="671" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671">
         <v>670</v>
       </c>
@@ -19581,10 +19598,10 @@
         <v>0</v>
       </c>
       <c r="K671" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="672" spans="1:11" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="672" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672">
         <v>671</v>
       </c>
@@ -19615,7 +19632,7 @@
       </c>
       <c r="K672" s="5"/>
     </row>
-    <row r="673" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673">
         <v>672</v>
       </c>
@@ -19646,7 +19663,7 @@
       </c>
       <c r="K673" s="5"/>
     </row>
-    <row r="674" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674">
         <v>673</v>
       </c>
@@ -19673,7 +19690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="675" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675">
         <v>674</v>
       </c>
@@ -19702,10 +19719,10 @@
         <v>2</v>
       </c>
       <c r="K675" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="676" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="676" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676">
         <v>675</v>
       </c>
@@ -19732,7 +19749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="677" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677">
         <v>676</v>
       </c>
@@ -19759,7 +19776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="678" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678">
         <v>677</v>
       </c>
@@ -19790,7 +19807,7 @@
       </c>
       <c r="K678" s="5"/>
     </row>
-    <row r="679" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679">
         <v>678</v>
       </c>
@@ -19817,7 +19834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="680" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680">
         <v>679</v>
       </c>
@@ -19844,7 +19861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="681" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681">
         <v>680</v>
       </c>
@@ -19875,7 +19892,7 @@
       </c>
       <c r="K681" s="5"/>
     </row>
-    <row r="682" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682">
         <v>681</v>
       </c>
@@ -19902,7 +19919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="683" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683">
         <v>682</v>
       </c>
@@ -19936,7 +19953,7 @@
       </c>
       <c r="K683" s="5"/>
     </row>
-    <row r="684" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684">
         <v>683</v>
       </c>
@@ -19963,7 +19980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="685" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685">
         <v>684</v>
       </c>
@@ -19990,7 +20007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="686" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686">
         <v>685</v>
       </c>
@@ -20019,7 +20036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="687" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687">
         <v>686</v>
       </c>
@@ -20046,7 +20063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="688" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688">
         <v>687</v>
       </c>
@@ -20077,7 +20094,7 @@
       </c>
       <c r="K688" s="5"/>
     </row>
-    <row r="689" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689">
         <v>688</v>
       </c>
@@ -20104,7 +20121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="690" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690">
         <v>689</v>
       </c>
@@ -20131,7 +20148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="691" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691">
         <v>690</v>
       </c>
@@ -20158,7 +20175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="692" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692">
         <v>691</v>
       </c>
@@ -20185,7 +20202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="693" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693">
         <v>692</v>
       </c>
@@ -20212,7 +20229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="694" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694">
         <v>693</v>
       </c>
@@ -20239,7 +20256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="695" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695">
         <v>694</v>
       </c>
@@ -20266,7 +20283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="696" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696">
         <v>695</v>
       </c>
@@ -20293,7 +20310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="697" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697">
         <v>696</v>
       </c>
@@ -20320,7 +20337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="698" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698">
         <v>697</v>
       </c>
@@ -20347,7 +20364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="699" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699">
         <v>698</v>
       </c>
@@ -20374,7 +20391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="700" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700">
         <v>699</v>
       </c>
@@ -20401,7 +20418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="701" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701">
         <v>700</v>
       </c>
@@ -20428,7 +20445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="702" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702">
         <v>701</v>
       </c>
@@ -20455,7 +20472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="703" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703">
         <v>702</v>
       </c>
@@ -20482,7 +20499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="704" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704">
         <v>703</v>
       </c>
@@ -20509,7 +20526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="705" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705">
         <v>704</v>
       </c>
@@ -20536,7 +20553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="706" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706">
         <v>705</v>
       </c>
@@ -20563,7 +20580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="707" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707">
         <v>706</v>
       </c>
@@ -20590,7 +20607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="708" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708">
         <v>707</v>
       </c>
@@ -20617,7 +20634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="709" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709">
         <v>708</v>
       </c>
@@ -20644,7 +20661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="710" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710">
         <v>709</v>
       </c>
@@ -20671,7 +20688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="711" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711">
         <v>710</v>
       </c>
@@ -20698,7 +20715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="712" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712">
         <v>711</v>
       </c>
@@ -20728,7 +20745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="713" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713">
         <v>712</v>
       </c>
@@ -20755,7 +20772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="714" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714">
         <v>713</v>
       </c>
@@ -20782,7 +20799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="715" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715">
         <v>714</v>
       </c>
@@ -20809,7 +20826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="716" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716">
         <v>715</v>
       </c>
@@ -20836,7 +20853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="717" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717">
         <v>716</v>
       </c>
@@ -20867,7 +20884,7 @@
       </c>
       <c r="K717" s="5"/>
     </row>
-    <row r="718" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718">
         <v>717</v>
       </c>
@@ -20900,10 +20917,10 @@
         <v>3</v>
       </c>
       <c r="K718" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="719" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="719" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719">
         <v>718</v>
       </c>
@@ -20930,7 +20947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="720" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720">
         <v>719</v>
       </c>
@@ -20964,7 +20981,7 @@
       </c>
       <c r="K720" s="5"/>
     </row>
-    <row r="721" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721">
         <v>720</v>
       </c>
@@ -20991,7 +21008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="722" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722">
         <v>721</v>
       </c>
@@ -21016,7 +21033,7 @@
       </c>
       <c r="K722" s="5"/>
     </row>
-    <row r="723" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723">
         <v>722</v>
       </c>
@@ -21043,7 +21060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="724" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724">
         <v>723</v>
       </c>
@@ -21070,7 +21087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="725" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725">
         <v>724</v>
       </c>
@@ -21097,7 +21114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="726" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726">
         <v>725</v>
       </c>
@@ -21124,7 +21141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="727" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727">
         <v>726</v>
       </c>
@@ -21151,7 +21168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="728" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728">
         <v>727</v>
       </c>
@@ -21178,7 +21195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="729" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729">
         <v>728</v>
       </c>
@@ -21205,7 +21222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="730" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730">
         <v>729</v>
       </c>
@@ -21232,7 +21249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="731" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731">
         <v>730</v>
       </c>
@@ -21259,7 +21276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="732" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732">
         <v>731</v>
       </c>
@@ -21286,7 +21303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="733" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733">
         <v>732</v>
       </c>
@@ -21313,7 +21330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="734" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734">
         <v>733</v>
       </c>
@@ -21340,7 +21357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="735" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735">
         <v>734</v>
       </c>
@@ -21367,7 +21384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="736" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736">
         <v>735</v>
       </c>
@@ -21394,7 +21411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="737" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737">
         <v>736</v>
       </c>
@@ -21421,7 +21438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="738" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738">
         <v>737</v>
       </c>
@@ -21448,7 +21465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="739" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739">
         <v>738</v>
       </c>
@@ -21482,7 +21499,7 @@
       </c>
       <c r="K739" s="5"/>
     </row>
-    <row r="740" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740">
         <v>739</v>
       </c>
@@ -21509,7 +21526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="741" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741">
         <v>740</v>
       </c>
@@ -21538,10 +21555,10 @@
         <v>1</v>
       </c>
       <c r="K741" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="742" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="742" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742">
         <v>741</v>
       </c>
@@ -21570,10 +21587,10 @@
         <v>1</v>
       </c>
       <c r="K742" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="743" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="743" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743">
         <v>742</v>
       </c>
@@ -21600,7 +21617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="744" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744">
         <v>743</v>
       </c>
@@ -21631,7 +21648,7 @@
       </c>
       <c r="K744" s="5"/>
     </row>
-    <row r="745" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745">
         <v>744</v>
       </c>
@@ -21658,7 +21675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="746" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746">
         <v>745</v>
       </c>
@@ -21685,7 +21702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="747" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747">
         <v>746</v>
       </c>
@@ -21718,10 +21735,10 @@
         <v>4</v>
       </c>
       <c r="K747" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="748" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="748" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748">
         <v>747</v>
       </c>
@@ -21748,7 +21765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="749" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749">
         <v>748</v>
       </c>
@@ -21775,7 +21792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="750" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750">
         <v>749</v>
       </c>
@@ -21802,7 +21819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="751" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751">
         <v>750</v>
       </c>
@@ -21816,7 +21833,7 @@
         <v>7</v>
       </c>
       <c r="E751" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I751" s="5">
         <v>1</v>
@@ -21827,7 +21844,7 @@
       </c>
       <c r="K751" s="5"/>
     </row>
-    <row r="752" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752">
         <v>751</v>
       </c>
@@ -21854,7 +21871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="753" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753">
         <v>752</v>
       </c>
@@ -21881,7 +21898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="754" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754">
         <v>753</v>
       </c>
@@ -21908,7 +21925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="755" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755">
         <v>754</v>
       </c>
@@ -21935,7 +21952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="756" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756">
         <v>755</v>
       </c>
@@ -21962,7 +21979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="757" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757">
         <v>756</v>
       </c>
@@ -21989,7 +22006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="758" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758">
         <v>757</v>
       </c>
@@ -22016,7 +22033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="759" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759">
         <v>758</v>
       </c>
@@ -22043,7 +22060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="760" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760">
         <v>759</v>
       </c>
@@ -22070,7 +22087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="761" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761">
         <v>760</v>
       </c>
@@ -22097,7 +22114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="762" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762">
         <v>761</v>
       </c>
@@ -22124,7 +22141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="763" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763">
         <v>762</v>
       </c>
@@ -22151,7 +22168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="764" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764">
         <v>763</v>
       </c>
@@ -22178,7 +22195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="765" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765">
         <v>764</v>
       </c>
@@ -22205,7 +22222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="766" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766">
         <v>765</v>
       </c>
@@ -22232,7 +22249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="767" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767">
         <v>766</v>
       </c>
@@ -22259,7 +22276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="768" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768">
         <v>767</v>
       </c>
@@ -22286,7 +22303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="769" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769">
         <v>768</v>
       </c>
@@ -22313,7 +22330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="770" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770">
         <v>769</v>
       </c>
@@ -22340,7 +22357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="771" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771">
         <v>770</v>
       </c>
@@ -22374,7 +22391,7 @@
       </c>
       <c r="K771" s="5"/>
     </row>
-    <row r="772" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772">
         <v>771</v>
       </c>
@@ -22408,7 +22425,7 @@
       </c>
       <c r="K772" s="5"/>
     </row>
-    <row r="773" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773">
         <v>772</v>
       </c>
@@ -22435,7 +22452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="774" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774">
         <v>773</v>
       </c>
@@ -22462,7 +22479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="775" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775">
         <v>774</v>
       </c>
@@ -22489,7 +22506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="776" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776">
         <v>775</v>
       </c>
@@ -22514,7 +22531,7 @@
       </c>
       <c r="K776" s="5"/>
     </row>
-    <row r="777" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777">
         <v>776</v>
       </c>
@@ -22541,7 +22558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="778" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778">
         <v>777</v>
       </c>
@@ -22568,7 +22585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="779" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779">
         <v>778</v>
       </c>
@@ -22602,7 +22619,7 @@
       </c>
       <c r="K779" s="5"/>
     </row>
-    <row r="780" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780">
         <v>779</v>
       </c>
@@ -22629,7 +22646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="781" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781">
         <v>780</v>
       </c>
@@ -22656,7 +22673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="782" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782">
         <v>781</v>
       </c>
@@ -22683,7 +22700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="783" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783">
         <v>782</v>
       </c>
@@ -22710,7 +22727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="784" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784">
         <v>783</v>
       </c>
@@ -22737,7 +22754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="785" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785">
         <v>784</v>
       </c>
@@ -22764,7 +22781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="786" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786">
         <v>785</v>
       </c>
@@ -22791,7 +22808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="787" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787">
         <v>786</v>
       </c>
@@ -22820,10 +22837,10 @@
         <v>1</v>
       </c>
       <c r="K787" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="788" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="788" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788">
         <v>787</v>
       </c>
@@ -22852,10 +22869,10 @@
         <v>1</v>
       </c>
       <c r="K788" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="789" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="789" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789">
         <v>788</v>
       </c>
@@ -22882,7 +22899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="790" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790">
         <v>789</v>
       </c>
@@ -22909,7 +22926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="791" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791">
         <v>790</v>
       </c>
@@ -22936,7 +22953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="792" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792">
         <v>791</v>
       </c>
@@ -22967,7 +22984,7 @@
       </c>
       <c r="K792" s="5"/>
     </row>
-    <row r="793" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793">
         <v>792</v>
       </c>
@@ -22994,7 +23011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="794" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794">
         <v>793</v>
       </c>
@@ -23021,7 +23038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="795" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795">
         <v>794</v>
       </c>
@@ -23048,7 +23065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="796" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796">
         <v>795</v>
       </c>
@@ -23075,7 +23092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="797" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797">
         <v>796</v>
       </c>
@@ -23102,7 +23119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="798" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798">
         <v>797</v>
       </c>
@@ -23129,7 +23146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="799" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799">
         <v>798</v>
       </c>
@@ -23156,7 +23173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="800" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800">
         <v>799</v>
       </c>
@@ -23183,7 +23200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="801" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801">
         <v>800</v>
       </c>
@@ -23213,7 +23230,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="802" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802">
         <v>801</v>
       </c>
@@ -23243,7 +23260,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="803" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803">
         <v>802</v>
       </c>
@@ -23270,7 +23287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="804" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804">
         <v>803</v>
       </c>
@@ -23297,7 +23314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="805" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805">
         <v>804</v>
       </c>
@@ -23322,7 +23339,7 @@
       </c>
       <c r="K805" s="5"/>
     </row>
-    <row r="806" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806">
         <v>805</v>
       </c>
@@ -23349,7 +23366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="807" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807">
         <v>806</v>
       </c>
@@ -23380,7 +23397,7 @@
       </c>
       <c r="K807" s="5"/>
     </row>
-    <row r="808" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808">
         <v>807</v>
       </c>
@@ -23407,7 +23424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="809" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809">
         <v>808</v>
       </c>
@@ -23434,7 +23451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="810" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810">
         <v>809</v>
       </c>
@@ -23461,7 +23478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="811" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811">
         <v>810</v>
       </c>
@@ -23488,7 +23505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="812" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812">
         <v>811</v>
       </c>
@@ -23519,7 +23536,7 @@
       </c>
       <c r="K812" s="5"/>
     </row>
-    <row r="813" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813">
         <v>812</v>
       </c>
@@ -23546,7 +23563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="814" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814">
         <v>813</v>
       </c>
@@ -23577,7 +23594,7 @@
       </c>
       <c r="K814" s="5"/>
     </row>
-    <row r="815" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" s="8">
         <v>814</v>
       </c>
@@ -23606,10 +23623,10 @@
         <v>1</v>
       </c>
       <c r="K815" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="816" spans="1:11" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="816" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816">
         <v>815</v>
       </c>
@@ -23636,7 +23653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="817" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A817">
         <v>816</v>
       </c>
@@ -23663,7 +23680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="818" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818">
         <v>817</v>
       </c>
@@ -23690,7 +23707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="819" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819">
         <v>818</v>
       </c>
@@ -23717,7 +23734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="820" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A820">
         <v>819</v>
       </c>
@@ -23744,7 +23761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="821" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821">
         <v>820</v>
       </c>
@@ -23771,7 +23788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="822" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822">
         <v>821</v>
       </c>
@@ -23798,7 +23815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="823" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823">
         <v>822</v>
       </c>
@@ -23825,7 +23842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="824" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824">
         <v>823</v>
       </c>
@@ -23852,7 +23869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="825" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825">
         <v>824</v>
       </c>
@@ -23879,7 +23896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="826" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826">
         <v>825</v>
       </c>
@@ -23910,7 +23927,7 @@
       </c>
       <c r="K826" s="5"/>
     </row>
-    <row r="827" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827">
         <v>826</v>
       </c>
@@ -23937,7 +23954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="828" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828">
         <v>827</v>
       </c>
@@ -23971,7 +23988,7 @@
       </c>
       <c r="K828" s="5"/>
     </row>
-    <row r="829" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829">
         <v>828</v>
       </c>
@@ -23998,7 +24015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="830" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830">
         <v>829</v>
       </c>
@@ -24025,7 +24042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="831" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831">
         <v>830</v>
       </c>
@@ -24052,7 +24069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="832" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832">
         <v>831</v>
       </c>
@@ -24079,7 +24096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="833" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833">
         <v>832</v>
       </c>
@@ -24104,7 +24121,7 @@
       </c>
       <c r="K833" s="5"/>
     </row>
-    <row r="834" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834">
         <v>833</v>
       </c>
@@ -24131,7 +24148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="835" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835">
         <v>834</v>
       </c>
@@ -24158,7 +24175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="836" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836">
         <v>835</v>
       </c>
@@ -24185,7 +24202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="837" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837">
         <v>836</v>
       </c>
@@ -24215,7 +24232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="838" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838">
         <v>837</v>
       </c>
@@ -24242,7 +24259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="839" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839">
         <v>838</v>
       </c>
@@ -24269,7 +24286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="840" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840">
         <v>839</v>
       </c>
@@ -24300,15 +24317,15 @@
         <v>2</v>
       </c>
       <c r="K840" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="841" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="841" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841">
         <v>840</v>
       </c>
       <c r="B841" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C841" t="s">
         <v>116</v>
@@ -24330,12 +24347,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="842" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842">
         <v>841</v>
       </c>
       <c r="B842" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C842" t="s">
         <v>106</v>
@@ -24357,12 +24374,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="843" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" s="8">
         <v>842</v>
       </c>
       <c r="B843" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C843" s="8" t="s">
         <v>107</v>
@@ -24386,15 +24403,15 @@
         <v>1</v>
       </c>
       <c r="K843" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="844" spans="1:11" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="844" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844">
         <v>843</v>
       </c>
       <c r="B844" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C844" t="s">
         <v>116</v>
@@ -24416,12 +24433,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="845" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845">
         <v>844</v>
       </c>
       <c r="B845" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C845" t="s">
         <v>116</v>
@@ -24443,12 +24460,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="846" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846">
         <v>845</v>
       </c>
       <c r="B846" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C846" t="s">
         <v>116</v>
@@ -24470,12 +24487,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="847" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847">
         <v>846</v>
       </c>
       <c r="B847" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C847" t="s">
         <v>116</v>
@@ -24497,12 +24514,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="848" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848">
         <v>847</v>
       </c>
       <c r="B848" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C848" t="s">
         <v>116</v>
@@ -24524,12 +24541,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="849" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849">
         <v>848</v>
       </c>
       <c r="B849" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C849" t="s">
         <v>116</v>
@@ -24551,12 +24568,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="850" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850">
         <v>849</v>
       </c>
       <c r="B850" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C850" t="s">
         <v>116</v>
@@ -24578,12 +24595,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="851" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851">
         <v>850</v>
       </c>
       <c r="B851" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C851" t="s">
         <v>116</v>
@@ -24605,12 +24622,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="852" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852">
         <v>851</v>
       </c>
       <c r="B852" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C852" s="2" t="s">
         <v>116</v>
@@ -24634,15 +24651,15 @@
         <v>1</v>
       </c>
       <c r="K852" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="853" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="853" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853">
         <v>852</v>
       </c>
       <c r="B853" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C853" t="s">
         <v>116</v>
@@ -24664,12 +24681,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="854" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854">
         <v>853</v>
       </c>
       <c r="B854" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C854" t="s">
         <v>116</v>
@@ -24691,12 +24708,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="855" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855">
         <v>854</v>
       </c>
       <c r="B855" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C855" t="s">
         <v>116</v>
@@ -24718,12 +24735,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="856" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856">
         <v>855</v>
       </c>
       <c r="B856" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C856" t="s">
         <v>116</v>
@@ -24749,12 +24766,12 @@
       </c>
       <c r="K856" s="5"/>
     </row>
-    <row r="857" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857">
         <v>856</v>
       </c>
       <c r="B857" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C857" s="2" t="s">
         <v>116</v>
@@ -24778,15 +24795,15 @@
         <v>1</v>
       </c>
       <c r="K857" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="858" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="858" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A858">
         <v>857</v>
       </c>
       <c r="B858" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C858" t="s">
         <v>116</v>
@@ -24808,12 +24825,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="859" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859">
         <v>858</v>
       </c>
       <c r="B859" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C859" t="s">
         <v>116</v>
@@ -24835,12 +24852,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="860" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A860">
         <v>859</v>
       </c>
       <c r="B860" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C860" t="s">
         <v>116</v>
@@ -24862,12 +24879,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="861" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861">
         <v>860</v>
       </c>
       <c r="B861" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C861" t="s">
         <v>116</v>
@@ -24887,12 +24904,12 @@
       </c>
       <c r="K861" s="5"/>
     </row>
-    <row r="862" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862">
         <v>861</v>
       </c>
       <c r="B862" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C862" s="3" t="s">
         <v>116</v>
@@ -24914,15 +24931,15 @@
         <v>1</v>
       </c>
       <c r="K862" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="863" spans="1:11" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="863" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863">
         <v>862</v>
       </c>
       <c r="B863" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C863" t="s">
         <v>116</v>
@@ -24947,12 +24964,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="864" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A864">
         <v>863</v>
       </c>
       <c r="B864" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C864" s="2" t="s">
         <v>116</v>
@@ -24976,15 +24993,15 @@
         <v>2</v>
       </c>
       <c r="K864" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="865" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="865" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A865">
         <v>864</v>
       </c>
       <c r="B865" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C865" t="s">
         <v>116</v>
@@ -25006,12 +25023,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="866" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A866">
         <v>865</v>
       </c>
       <c r="B866" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C866" t="s">
         <v>116</v>
@@ -25036,12 +25053,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="867" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867">
         <v>866</v>
       </c>
       <c r="B867" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C867" t="s">
         <v>116</v>
@@ -25063,12 +25080,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="868" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868">
         <v>867</v>
       </c>
       <c r="B868" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C868" t="s">
         <v>116</v>
@@ -25097,12 +25114,12 @@
       </c>
       <c r="K868" s="5"/>
     </row>
-    <row r="869" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869">
         <v>868</v>
       </c>
       <c r="B869" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C869" t="s">
         <v>106</v>
@@ -25124,12 +25141,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="870" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870">
         <v>869</v>
       </c>
       <c r="B870" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C870" t="s">
         <v>106</v>
@@ -25151,12 +25168,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="871" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A871">
         <v>870</v>
       </c>
       <c r="B871" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C871" t="s">
         <v>106</v>
@@ -25176,12 +25193,12 @@
       </c>
       <c r="K871" s="5"/>
     </row>
-    <row r="872" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A872">
         <v>871</v>
       </c>
       <c r="B872" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C872" t="s">
         <v>106</v>
@@ -25203,12 +25220,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="873" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873">
         <v>872</v>
       </c>
       <c r="B873" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C873" t="s">
         <v>106</v>
@@ -25230,12 +25247,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="874" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874">
         <v>873</v>
       </c>
       <c r="B874" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C874" t="s">
         <v>106</v>
@@ -25260,12 +25277,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="875" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875">
         <v>874</v>
       </c>
       <c r="B875" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C875" t="s">
         <v>106</v>
@@ -25294,12 +25311,12 @@
       </c>
       <c r="K875" s="5"/>
     </row>
-    <row r="876" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876">
         <v>875</v>
       </c>
       <c r="B876" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C876" t="s">
         <v>106</v>
@@ -25324,12 +25341,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="877" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877">
         <v>876</v>
       </c>
       <c r="B877" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C877" t="s">
         <v>106</v>
@@ -25351,12 +25368,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="878" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878">
         <v>877</v>
       </c>
       <c r="B878" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C878" t="s">
         <v>106</v>
@@ -25376,12 +25393,12 @@
       </c>
       <c r="K878" s="5"/>
     </row>
-    <row r="879" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879">
         <v>878</v>
       </c>
       <c r="B879" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C879" t="s">
         <v>107</v>
@@ -25403,12 +25420,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="880" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880">
         <v>879</v>
       </c>
       <c r="B880" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C880" t="s">
         <v>107</v>
@@ -25430,12 +25447,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="881" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881">
         <v>880</v>
       </c>
       <c r="B881" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C881" t="s">
         <v>107</v>
@@ -25457,12 +25474,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="882" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882">
         <v>881</v>
       </c>
       <c r="B882" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C882" t="s">
         <v>107</v>
@@ -25482,12 +25499,12 @@
       </c>
       <c r="K882" s="5"/>
     </row>
-    <row r="883" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883">
         <v>882</v>
       </c>
       <c r="B883" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C883" t="s">
         <v>107</v>
@@ -25509,12 +25526,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="884" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884">
         <v>883</v>
       </c>
       <c r="B884" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C884" t="s">
         <v>107</v>
@@ -25536,12 +25553,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="885" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885">
         <v>884</v>
       </c>
       <c r="B885" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C885" t="s">
         <v>107</v>
@@ -25563,12 +25580,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="886" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886">
         <v>885</v>
       </c>
       <c r="B886" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C886" t="s">
         <v>107</v>
@@ -25594,12 +25611,12 @@
       </c>
       <c r="K886" s="5"/>
     </row>
-    <row r="887" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887">
         <v>886</v>
       </c>
       <c r="B887" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C887" t="s">
         <v>107</v>
@@ -25621,12 +25638,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="888" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888">
         <v>887</v>
       </c>
       <c r="B888" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C888" t="s">
         <v>107</v>
